--- a/research/traditional_assets/database/data/kuwait/kuwait_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ18"/>
+  <dimension ref="A1:AQ16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.175</v>
+        <v>0.08810000000000001</v>
       </c>
       <c r="E2">
-        <v>0.222</v>
+        <v>-0.025</v>
       </c>
       <c r="G2">
-        <v>0.05913314431687393</v>
+        <v>0.5042493988227451</v>
       </c>
       <c r="H2">
-        <v>0.05913314431687393</v>
+        <v>0.5042493988227451</v>
       </c>
       <c r="I2">
-        <v>0.474990876680796</v>
+        <v>0.5213468529618944</v>
       </c>
       <c r="J2">
-        <v>0.4714711286682087</v>
+        <v>0.5135542678566242</v>
       </c>
       <c r="K2">
-        <v>117.65</v>
+        <v>170.683</v>
       </c>
       <c r="L2">
-        <v>0.3302641551806417</v>
+        <v>0.46065426437765</v>
       </c>
       <c r="M2">
-        <v>15.578</v>
+        <v>66.788</v>
       </c>
       <c r="N2">
-        <v>0.006408062525709585</v>
+        <v>0.03519789196310935</v>
       </c>
       <c r="O2">
-        <v>0.1324096897577561</v>
+        <v>0.3912984890117938</v>
       </c>
       <c r="P2">
-        <v>8.878</v>
+        <v>50.46</v>
       </c>
       <c r="Q2">
-        <v>0.003651995063759769</v>
+        <v>0.02659288537549407</v>
       </c>
       <c r="R2">
-        <v>0.07546111347216321</v>
+        <v>0.2956357692330226</v>
       </c>
       <c r="S2">
-        <v>6.7</v>
+        <v>16.328</v>
       </c>
       <c r="T2">
-        <v>0.4300937219155219</v>
+        <v>0.2444750553991735</v>
       </c>
       <c r="U2">
-        <v>349.553</v>
+        <v>251.032</v>
       </c>
       <c r="V2">
-        <v>0.1437897984368573</v>
+        <v>0.1322961791831357</v>
       </c>
       <c r="W2">
-        <v>0.002260691409091989</v>
+        <v>0.03762575527002435</v>
       </c>
       <c r="X2">
-        <v>0.05183094072871679</v>
+        <v>0.08415990584839494</v>
       </c>
       <c r="Y2">
-        <v>-0.0495702493196248</v>
+        <v>-0.0465341505783706</v>
       </c>
       <c r="Z2">
-        <v>0.1223461837524763</v>
+        <v>0.1205906590187752</v>
       </c>
       <c r="AA2">
-        <v>0.01006109683624708</v>
+        <v>0.03662444954766091</v>
       </c>
       <c r="AB2">
-        <v>0.04936048212955021</v>
+        <v>0.07972793063253869</v>
       </c>
       <c r="AC2">
-        <v>-0.04102055517869923</v>
+        <v>-0.04287141938319128</v>
       </c>
       <c r="AD2">
-        <v>717.1089999999999</v>
+        <v>779.715</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>717.1089999999999</v>
+        <v>779.715</v>
       </c>
       <c r="AG2">
-        <v>367.5559999999999</v>
+        <v>528.683</v>
       </c>
       <c r="AH2">
-        <v>0.2277903973464705</v>
+        <v>0.2912410844851833</v>
       </c>
       <c r="AI2">
-        <v>0.1841049891030007</v>
+        <v>0.2169059299555041</v>
       </c>
       <c r="AJ2">
-        <v>0.1313377327450299</v>
+        <v>0.2179073054258479</v>
       </c>
       <c r="AK2">
-        <v>0.1036666745638766</v>
+        <v>0.158113971928559</v>
       </c>
       <c r="AL2">
-        <v>21.384</v>
+        <v>23.265</v>
       </c>
       <c r="AM2">
-        <v>20.632</v>
+        <v>22.46</v>
       </c>
       <c r="AN2">
-        <v>3.855839337563179</v>
+        <v>4.531724951614872</v>
       </c>
       <c r="AO2">
-        <v>7.912738496071829</v>
+        <v>8.303073286052008</v>
       </c>
       <c r="AP2">
-        <v>1.976320034412302</v>
+        <v>3.07272008694793</v>
       </c>
       <c r="AQ2">
-        <v>8.201143854207055</v>
+        <v>8.6006678539626</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Gulf Investment House K.S.C.P. (KWSE:GIH)</t>
+          <t>Noor Financial Investment Company - KPSC (KWSE:NOOR)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,109 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.451</v>
+        <v>0.051</v>
+      </c>
+      <c r="E3">
+        <v>0.262</v>
       </c>
       <c r="G3">
-        <v>0.01463350785340314</v>
+        <v>0.5253955037468776</v>
       </c>
       <c r="H3">
-        <v>0.01463350785340314</v>
+        <v>0.5253955037468776</v>
       </c>
       <c r="I3">
-        <v>0.5445026178010471</v>
+        <v>0.5220649458784347</v>
       </c>
       <c r="J3">
-        <v>0.5394154806676007</v>
+        <v>0.5104248955044396</v>
       </c>
       <c r="K3">
-        <v>20.4</v>
+        <v>58.4</v>
       </c>
       <c r="L3">
-        <v>0.5340314136125653</v>
+        <v>0.4862614487926728</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>7.71</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.02623341272541681</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.1320205479452055</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>7.71</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.02623341272541681</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.1320205479452055</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>67</v>
+        <v>31.1</v>
       </c>
       <c r="V3">
-        <v>0.1662118580997271</v>
+        <v>0.1058183055461041</v>
       </c>
       <c r="W3">
-        <v>0.1763180639585134</v>
+        <v>0.2102988836874325</v>
       </c>
       <c r="X3">
-        <v>0.04887865283753826</v>
+        <v>0.08556531849718776</v>
       </c>
       <c r="Y3">
-        <v>0.1274394111209751</v>
+        <v>0.1247335651902447</v>
       </c>
       <c r="Z3">
-        <v>0.4945624029000518</v>
+        <v>0.4038739617311767</v>
       </c>
       <c r="AA3">
-        <v>0.266774616280455</v>
+        <v>0.2061473247135999</v>
       </c>
       <c r="AB3">
-        <v>0.04887865283753826</v>
+        <v>0.07978350142112527</v>
       </c>
       <c r="AC3">
-        <v>0.2178959634429168</v>
+        <v>0.1263638232924746</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>52.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>52.7</v>
       </c>
       <c r="AG3">
-        <v>-67</v>
+        <v>21.6</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.1520484708597807</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.1639701306782825</v>
       </c>
       <c r="AJ3">
-        <v>-0.199345432906873</v>
+        <v>0.06846275752773376</v>
       </c>
       <c r="AK3">
-        <v>-0.7030430220356767</v>
+        <v>0.07440578711677576</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>0.8247261345852895</v>
+      </c>
+      <c r="AO3">
+        <v>22.15547703180212</v>
       </c>
       <c r="AP3">
-        <v>-3.130841121495327</v>
+        <v>0.3380281690140846</v>
+      </c>
+      <c r="AQ3">
+        <v>22.15547703180212</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Noor Financial Investment Company - KPSC (KWSE:NOOR)</t>
+          <t>Asiya Capital Investments Company K.S.C.P. (KWSE:ASIYA)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,121 +856,103 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0403</v>
-      </c>
-      <c r="E4">
-        <v>0.643</v>
+        <v>0.578</v>
       </c>
       <c r="G4">
-        <v>0.4289746001881468</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>0.4289746001881468</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0.5211665098777046</v>
+        <v>0.89086859688196</v>
       </c>
       <c r="J4">
-        <v>0.5173496484581662</v>
+        <v>0.8816696529743067</v>
       </c>
       <c r="K4">
-        <v>53.4</v>
+        <v>39.5</v>
       </c>
       <c r="L4">
-        <v>0.5023518344308561</v>
+        <v>0.8797327394209354</v>
       </c>
       <c r="M4">
-        <v>7.94</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.0184995340167754</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.148689138576779</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>7.94</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.0184995340167754</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.148689138576779</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>35.4</v>
+        <v>5.88</v>
       </c>
       <c r="V4">
-        <v>0.08247903075489282</v>
+        <v>0.04074844074844074</v>
       </c>
       <c r="W4">
-        <v>0.2558696693818879</v>
+        <v>0.1639684516396845</v>
       </c>
       <c r="X4">
-        <v>0.05315332089175748</v>
+        <v>0.07938024802941726</v>
       </c>
       <c r="Y4">
-        <v>0.2027163484901304</v>
+        <v>0.08458820361026725</v>
       </c>
       <c r="Z4">
-        <v>0.3864049436568521</v>
+        <v>0.2156580211335255</v>
       </c>
       <c r="AA4">
-        <v>0.19990646176337</v>
+        <v>0.1901391326539211</v>
       </c>
       <c r="AB4">
-        <v>0.05000501190661265</v>
+        <v>0.07938024802941726</v>
       </c>
       <c r="AC4">
-        <v>0.1499014498567573</v>
+        <v>0.1107588846245038</v>
       </c>
       <c r="AD4">
-        <v>63.9</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>63.9</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>28.5</v>
+        <v>-5.88</v>
       </c>
       <c r="AH4">
-        <v>0.1295883187994322</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.1829373031777842</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>0.0622678610443522</v>
+        <v>-0.04247941048981361</v>
       </c>
       <c r="AK4">
-        <v>0.09079324625676968</v>
+        <v>-0.02194684980591221</v>
       </c>
       <c r="AL4">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>2.892</v>
-      </c>
-      <c r="AN4">
-        <v>1.123022847100176</v>
-      </c>
-      <c r="AO4">
-        <v>17.15170278637771</v>
-      </c>
-      <c r="AP4">
-        <v>0.5008787346221442</v>
-      </c>
-      <c r="AQ4">
-        <v>19.15629322268326</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -969,7 +963,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kuwait Financial Centre - K.P.S.C (KWSE:MARKAZ)</t>
+          <t>Al-Deera Holding Company K.P.S.C. (KWSE:ALDEERA)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -978,121 +972,109 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.297</v>
-      </c>
-      <c r="E5">
-        <v>0.575</v>
+        <v>0.625</v>
       </c>
       <c r="G5">
-        <v>0.07912087912087912</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>0.07912087912087912</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>0.6776556776556777</v>
+        <v>0.825938566552901</v>
       </c>
       <c r="J5">
-        <v>0.6728288300605564</v>
+        <v>0.825938566552901</v>
       </c>
       <c r="K5">
-        <v>60</v>
+        <v>3.93</v>
       </c>
       <c r="L5">
-        <v>0.5494505494505494</v>
+        <v>0.6706484641638225</v>
       </c>
       <c r="M5">
-        <v>0.54</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.00188745193988116</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.009000000000000001</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>0.54</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.00188745193988116</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.009000000000000001</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>39.7</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="V5">
-        <v>0.1387626703949668</v>
+        <v>0.01688935281837161</v>
       </c>
       <c r="W5">
-        <v>0.2106002106002106</v>
+        <v>0.08204592901878915</v>
       </c>
       <c r="X5">
-        <v>0.06850828870181337</v>
+        <v>0.0991832396304116</v>
       </c>
       <c r="Y5">
-        <v>0.1420919218983973</v>
+        <v>-0.01713731061162245</v>
       </c>
       <c r="Z5">
-        <v>0.2468354430379747</v>
+        <v>0.08446238108965121</v>
       </c>
       <c r="AA5">
-        <v>0.1660780023567196</v>
+        <v>0.06976073796483137</v>
       </c>
       <c r="AB5">
-        <v>0.05081421816984393</v>
+        <v>0.08391269193467768</v>
       </c>
       <c r="AC5">
-        <v>0.1152637841868757</v>
+        <v>-0.01415195396984631</v>
       </c>
       <c r="AD5">
-        <v>195.6</v>
+        <v>27.5</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>195.6</v>
+        <v>27.5</v>
       </c>
       <c r="AG5">
-        <v>155.9</v>
+        <v>26.691</v>
       </c>
       <c r="AH5">
-        <v>0.406061864230849</v>
+        <v>0.3647214854111406</v>
       </c>
       <c r="AI5">
-        <v>0.3055772535541321</v>
+        <v>0.3973988439306358</v>
       </c>
       <c r="AJ5">
-        <v>0.3527149321266968</v>
+        <v>0.3578313737582282</v>
       </c>
       <c r="AK5">
-        <v>0.2596602265156562</v>
+        <v>0.3902706496468833</v>
       </c>
       <c r="AL5">
-        <v>8.67</v>
+        <v>0.886</v>
       </c>
       <c r="AM5">
-        <v>8.67</v>
-      </c>
-      <c r="AN5">
-        <v>2.445</v>
+        <v>0.886</v>
       </c>
       <c r="AO5">
-        <v>8.535178777393311</v>
-      </c>
-      <c r="AP5">
-        <v>1.94875</v>
+        <v>5.4627539503386</v>
       </c>
       <c r="AQ5">
-        <v>8.535178777393311</v>
+        <v>5.4627539503386</v>
       </c>
     </row>
     <row r="6">
@@ -1112,118 +1094,118 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.121</v>
+        <v>0.117</v>
       </c>
       <c r="G6">
-        <v>-0.225</v>
+        <v>0.5125628140703518</v>
       </c>
       <c r="H6">
-        <v>-0.225</v>
+        <v>0.5125628140703518</v>
       </c>
       <c r="I6">
-        <v>0.4411111111111111</v>
+        <v>0.3331658291457287</v>
       </c>
       <c r="J6">
-        <v>0.4379863570772662</v>
+        <v>0.3314805545235908</v>
       </c>
       <c r="K6">
-        <v>8.35</v>
+        <v>5.27</v>
       </c>
       <c r="L6">
-        <v>0.4638888888888889</v>
+        <v>0.2648241206030151</v>
       </c>
       <c r="M6">
-        <v>5.44</v>
+        <v>4.91</v>
       </c>
       <c r="N6">
-        <v>0.04986251145737856</v>
+        <v>0.0724188790560472</v>
       </c>
       <c r="O6">
-        <v>0.6514970059880241</v>
+        <v>0.9316888045540798</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>4.91</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.0724188790560472</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.9316888045540798</v>
       </c>
       <c r="S6">
-        <v>5.44</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>5.45</v>
+        <v>8.5</v>
       </c>
       <c r="V6">
-        <v>0.04995417048579286</v>
+        <v>0.1253687315634218</v>
       </c>
       <c r="W6">
-        <v>0.1084415584415584</v>
+        <v>0.06288782816229117</v>
       </c>
       <c r="X6">
-        <v>0.05253671684556314</v>
+        <v>0.1412441777686587</v>
       </c>
       <c r="Y6">
-        <v>0.05590484159599529</v>
+        <v>-0.07835634960636752</v>
       </c>
       <c r="Z6">
-        <v>0.3428571428571429</v>
+        <v>0.2157181571815718</v>
       </c>
       <c r="AA6">
-        <v>0.1501667509979198</v>
+        <v>0.07150637436335452</v>
       </c>
       <c r="AB6">
-        <v>0.04941732597609653</v>
+        <v>0.08735881124099966</v>
       </c>
       <c r="AC6">
-        <v>0.1007494250218233</v>
+        <v>-0.01585243687764513</v>
       </c>
       <c r="AD6">
-        <v>13.9</v>
+        <v>121.6</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>13.9</v>
+        <v>121.6</v>
       </c>
       <c r="AG6">
-        <v>8.449999999999999</v>
+        <v>113.1</v>
       </c>
       <c r="AH6">
-        <v>0.1130081300813008</v>
+        <v>0.6420274551214361</v>
       </c>
       <c r="AI6">
-        <v>0.1416921508664628</v>
+        <v>0.5871559633027523</v>
       </c>
       <c r="AJ6">
-        <v>0.07188430455125477</v>
+        <v>0.6252072968490879</v>
       </c>
       <c r="AK6">
-        <v>0.09120345385860765</v>
+        <v>0.5694864048338368</v>
       </c>
       <c r="AL6">
-        <v>0.03</v>
+        <v>1.71</v>
       </c>
       <c r="AM6">
-        <v>0.03</v>
+        <v>1.71</v>
       </c>
       <c r="AN6">
-        <v>1.741854636591479</v>
+        <v>16.04221635883905</v>
       </c>
       <c r="AO6">
-        <v>264.6666666666667</v>
+        <v>3.87719298245614</v>
       </c>
       <c r="AP6">
-        <v>1.058897243107769</v>
+        <v>14.92084432717678</v>
       </c>
       <c r="AQ6">
-        <v>264.6666666666667</v>
+        <v>3.87719298245614</v>
       </c>
     </row>
     <row r="7">
@@ -1234,7 +1216,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Coast Investment &amp; Development Company K.S.C.P. (KWSE:COAST)</t>
+          <t>International Financial Advisors Holding - KPSC (KWSE:IFA)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1243,25 +1225,28 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.236</v>
+        <v>-0.145</v>
+      </c>
+      <c r="E7">
+        <v>-0.025</v>
       </c>
       <c r="G7">
-        <v>-0.8535031847133758</v>
+        <v>0.2655172413793104</v>
       </c>
       <c r="H7">
-        <v>-0.8535031847133758</v>
+        <v>0.2655172413793104</v>
       </c>
       <c r="I7">
-        <v>0.6942675159235669</v>
+        <v>0.7931034482758621</v>
       </c>
       <c r="J7">
-        <v>0.6942675159235669</v>
+        <v>0.7751793103448277</v>
       </c>
       <c r="K7">
-        <v>-9.960000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="L7">
-        <v>-0.6343949044585988</v>
+        <v>0.6682758620689655</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1270,7 +1255,7 @@
         <v>-0</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P7">
         <v>-0</v>
@@ -1279,73 +1264,79 @@
         <v>-0</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
       <c r="U7">
-        <v>13.5</v>
+        <v>2.83</v>
       </c>
       <c r="V7">
-        <v>0.08364312267657992</v>
+        <v>0.03511166253101737</v>
       </c>
       <c r="W7">
-        <v>-0.05886524822695036</v>
+        <v>0.1050976138828633</v>
       </c>
       <c r="X7">
-        <v>0.04887865283753826</v>
+        <v>0.1194368799552292</v>
       </c>
       <c r="Y7">
-        <v>-0.1077439010644886</v>
+        <v>-0.01433926607236584</v>
       </c>
       <c r="Z7">
-        <v>0.1014867485455721</v>
+        <v>0.07736634297300182</v>
       </c>
       <c r="AA7">
-        <v>0.070458952811894</v>
+        <v>0.05997278838971295</v>
       </c>
       <c r="AB7">
-        <v>0.04887865283753826</v>
+        <v>0.0808052769230069</v>
       </c>
       <c r="AC7">
-        <v>0.02158029997435575</v>
+        <v>-0.02083248853329395</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AG7">
-        <v>-13.5</v>
+        <v>90.77</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>0.5373134328358209</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>0.4027538726333907</v>
       </c>
       <c r="AJ7">
-        <v>-0.09127789046653144</v>
+        <v>0.5296726381513683</v>
       </c>
       <c r="AK7">
-        <v>-0.09084791386271872</v>
+        <v>0.3953913838916235</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>8.139130434782608</v>
+      </c>
+      <c r="AO7">
+        <v>5.693069306930693</v>
       </c>
       <c r="AP7">
-        <v>-1.227272727272727</v>
+        <v>7.89304347826087</v>
+      </c>
+      <c r="AQ7">
+        <v>5.693069306930693</v>
       </c>
     </row>
     <row r="8">
@@ -1356,7 +1347,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gulf North Africa Holding Company - KPSC (KWSE:GNAHC)</t>
+          <t>Tamdeen Investment Company - KSCP (KWSE:TAMINV)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1365,118 +1356,121 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.319</v>
+        <v>0.08810000000000001</v>
       </c>
       <c r="E8">
-        <v>-0.0458</v>
+        <v>0.177</v>
       </c>
       <c r="G8">
-        <v>0.1358148893360161</v>
+        <v>0.5567970204841712</v>
       </c>
       <c r="H8">
-        <v>0.1358148893360161</v>
+        <v>0.5567970204841712</v>
       </c>
       <c r="I8">
-        <v>0.1871227364185111</v>
+        <v>0.8733705772811917</v>
       </c>
       <c r="J8">
-        <v>0.1867006550581686</v>
+        <v>0.8680679702048416</v>
       </c>
       <c r="K8">
-        <v>0.696</v>
+        <v>42</v>
       </c>
       <c r="L8">
-        <v>0.07002012072434607</v>
+        <v>0.7821229050279329</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>20.39</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.03054224086279209</v>
       </c>
       <c r="O8">
-        <v>-0</v>
+        <v>0.4854761904761905</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>10.9</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.01632714200119832</v>
       </c>
       <c r="R8">
-        <v>-0</v>
+        <v>0.2595238095238095</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>9.49</v>
+      </c>
+      <c r="T8">
+        <v>0.4654242275625307</v>
       </c>
       <c r="U8">
-        <v>10.7</v>
+        <v>118.9</v>
       </c>
       <c r="V8">
-        <v>0.2505854800936768</v>
+        <v>0.1781006590772918</v>
       </c>
       <c r="W8">
-        <v>0.01938718662952646</v>
+        <v>0.04570184983677911</v>
       </c>
       <c r="X8">
-        <v>0.05580446327296326</v>
+        <v>0.0863605248156038</v>
       </c>
       <c r="Y8">
-        <v>-0.0364172766434368</v>
+        <v>-0.04065867497882469</v>
       </c>
       <c r="Z8">
-        <v>0.2679245283018868</v>
+        <v>0.04813984760197221</v>
       </c>
       <c r="AA8">
-        <v>0.05002168494011309</v>
+        <v>0.04178865979381443</v>
       </c>
       <c r="AB8">
-        <v>0.05107110297053279</v>
+        <v>0.08147182174715134</v>
       </c>
       <c r="AC8">
-        <v>-0.001049418030419698</v>
+        <v>-0.03968316195333691</v>
       </c>
       <c r="AD8">
-        <v>10.3</v>
+        <v>135.1</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>10.3</v>
+        <v>135.1</v>
       </c>
       <c r="AG8">
-        <v>-0.3999999999999986</v>
+        <v>16.19999999999999</v>
       </c>
       <c r="AH8">
-        <v>0.1943396226415094</v>
+        <v>0.1683069639965118</v>
       </c>
       <c r="AI8">
-        <v>0.1570121951219512</v>
+        <v>0.1154700854700855</v>
       </c>
       <c r="AJ8">
-        <v>-0.009456264775413677</v>
+        <v>0.02369113775957881</v>
       </c>
       <c r="AK8">
-        <v>-0.007285974499089227</v>
+        <v>0.01541242507848919</v>
       </c>
       <c r="AL8">
-        <v>0.245</v>
+        <v>6.4</v>
       </c>
       <c r="AM8">
-        <v>0.245</v>
+        <v>6.4</v>
       </c>
       <c r="AN8">
-        <v>3.093093093093093</v>
+        <v>2.553875236294896</v>
       </c>
       <c r="AO8">
-        <v>7.591836734693878</v>
+        <v>7.328124999999999</v>
       </c>
       <c r="AP8">
-        <v>-0.1201201201201197</v>
+        <v>0.3062381852551983</v>
       </c>
       <c r="AQ8">
-        <v>7.591836734693878</v>
+        <v>7.328124999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1487,7 +1481,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Al-Deera Holding Company K.P.S.C. (KWSE:ALDEERA)</t>
+          <t>Coast Investment &amp; Development Company K.S.C.P. (KWSE:COAST)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1495,107 +1489,116 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D9">
+        <v>0.213</v>
+      </c>
+      <c r="E9">
+        <v>-0.0173</v>
+      </c>
       <c r="G9">
-        <v>0</v>
+        <v>1.322645290581162</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1.322645290581162</v>
       </c>
       <c r="I9">
-        <v>0.6765578635014836</v>
+        <v>0.5501002004008017</v>
       </c>
       <c r="J9">
-        <v>0.6765578635014836</v>
+        <v>0.5464480828877673</v>
       </c>
       <c r="K9">
-        <v>1.71</v>
+        <v>4.79</v>
       </c>
       <c r="L9">
-        <v>0.5074183976261127</v>
+        <v>0.4799599198396793</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>7.19</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.05643642072213501</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>1.501043841336117</v>
       </c>
       <c r="P9">
-        <v>-0</v>
+        <v>7.19</v>
       </c>
       <c r="Q9">
-        <v>-0</v>
+        <v>0.05643642072213501</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>1.501043841336117</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
       <c r="U9">
-        <v>4.42</v>
+        <v>3.13</v>
       </c>
       <c r="V9">
-        <v>0.0728171334431631</v>
+        <v>0.02456828885400314</v>
       </c>
       <c r="W9">
-        <v>0.15</v>
+        <v>0.02954966070326959</v>
       </c>
       <c r="X9">
-        <v>0.06112967494986782</v>
+        <v>0.07938024802941726</v>
       </c>
       <c r="Y9">
-        <v>0.08887032505013218</v>
+        <v>-0.04983058732614767</v>
       </c>
       <c r="Z9">
-        <v>0.06114820728697925</v>
+        <v>0.06716016150740242</v>
       </c>
       <c r="AA9">
-        <v>0.04137030047902453</v>
+        <v>0.03669954150215288</v>
       </c>
       <c r="AB9">
-        <v>0.05225269294781156</v>
+        <v>0.07938024802941726</v>
       </c>
       <c r="AC9">
-        <v>-0.01088239246878703</v>
+        <v>-0.04268070652726438</v>
       </c>
       <c r="AD9">
-        <v>25.9</v>
+        <v>0</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>25.9</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>21.48</v>
+        <v>-3.13</v>
       </c>
       <c r="AH9">
-        <v>0.2990762124711316</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>0.3471849865951743</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>0.2613774641031881</v>
+        <v>-0.02518709262090609</v>
       </c>
       <c r="AK9">
-        <v>0.3060701054431461</v>
+        <v>-0.02193873974907128</v>
       </c>
       <c r="AL9">
-        <v>0.58</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>0.58</v>
-      </c>
-      <c r="AO9">
-        <v>3.931034482758621</v>
-      </c>
-      <c r="AQ9">
-        <v>3.931034482758621</v>
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>-0.5670289855072465</v>
       </c>
     </row>
     <row r="10">
@@ -1606,7 +1609,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Al Bareeq Holding Company - K.S.C.P. (KWSE:BAREEQ)</t>
+          <t>First Investment Company K.S.C.P. (KWSE:ALOLA)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1614,23 +1617,29 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D10">
+        <v>-0.07719999999999999</v>
+      </c>
+      <c r="E10">
+        <v>-0.0322</v>
+      </c>
       <c r="G10">
-        <v>0.2412280701754386</v>
+        <v>0.08610619469026548</v>
       </c>
       <c r="H10">
-        <v>0.2412280701754386</v>
+        <v>0.08610619469026548</v>
       </c>
       <c r="I10">
-        <v>0.1929824561403509</v>
+        <v>0.4053097345132743</v>
       </c>
       <c r="J10">
-        <v>0.1929824561403509</v>
+        <v>0.4053097345132743</v>
       </c>
       <c r="K10">
-        <v>-0.468</v>
+        <v>1.28</v>
       </c>
       <c r="L10">
-        <v>-0.06842105263157895</v>
+        <v>0.1132743362831858</v>
       </c>
       <c r="M10">
         <v>-0</v>
@@ -1639,7 +1648,7 @@
         <v>-0</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P10">
         <v>-0</v>
@@ -1648,73 +1657,79 @@
         <v>-0</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
       <c r="U10">
-        <v>0.431</v>
+        <v>26.4</v>
       </c>
       <c r="V10">
-        <v>0.008304431599229287</v>
+        <v>0.2885245901639344</v>
       </c>
       <c r="W10">
-        <v>-0.003122081387591728</v>
+        <v>0.008210391276459268</v>
       </c>
       <c r="X10">
-        <v>0.04887865283753826</v>
+        <v>0.08267500936942318</v>
       </c>
       <c r="Y10">
-        <v>-0.05200073422512998</v>
+        <v>-0.07446461809296391</v>
       </c>
       <c r="Z10">
-        <v>0.04678938619713106</v>
+        <v>0.09017636262070065</v>
       </c>
       <c r="AA10">
-        <v>0.009029530669621786</v>
+        <v>0.03654935759316894</v>
       </c>
       <c r="AB10">
-        <v>0.04887865283753826</v>
+        <v>0.07961148983228711</v>
       </c>
       <c r="AC10">
-        <v>-0.03984912216791647</v>
+        <v>-0.04306213223911817</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>8.74</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>8.74</v>
       </c>
       <c r="AG10">
-        <v>-0.431</v>
+        <v>-17.66</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>0.08719074221867519</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>0.04967602591792657</v>
       </c>
       <c r="AJ10">
-        <v>-0.008373972682585634</v>
+        <v>-0.2391657638136511</v>
       </c>
       <c r="AK10">
-        <v>-0.002868189713114482</v>
+        <v>-0.1180954928447238</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>0.593</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>0.593</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>1.571942446043166</v>
+      </c>
+      <c r="AO10">
+        <v>7.723440134907252</v>
       </c>
       <c r="AP10">
-        <v>-0.3013986013986014</v>
+        <v>-3.176258992805755</v>
+      </c>
+      <c r="AQ10">
+        <v>7.723440134907252</v>
       </c>
     </row>
     <row r="11">
@@ -1725,7 +1740,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tamdeen Investment Company - KSCP (KWSE:TAMINV)</t>
+          <t>Kuwait Financial Centre - KPSC (KWSE:MARKAZ)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1734,121 +1749,121 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.155</v>
+        <v>-0.0247</v>
       </c>
       <c r="E11">
-        <v>-0.39</v>
+        <v>-0.273</v>
       </c>
       <c r="G11">
-        <v>-0.4008733624454149</v>
+        <v>1.226381461675579</v>
       </c>
       <c r="H11">
-        <v>-0.4008733624454149</v>
+        <v>1.226381461675579</v>
       </c>
       <c r="I11">
-        <v>0.4716157205240175</v>
+        <v>0.303030303030303</v>
       </c>
       <c r="J11">
-        <v>0.4488411152166611</v>
+        <v>0.3000259000259</v>
       </c>
       <c r="K11">
-        <v>2.83</v>
+        <v>5.56</v>
       </c>
       <c r="L11">
-        <v>0.1235807860262009</v>
+        <v>0.09910873440285205</v>
       </c>
       <c r="M11">
-        <v>0.292</v>
+        <v>15.458</v>
       </c>
       <c r="N11">
-        <v>0.0006819243344231668</v>
+        <v>0.089976717112922</v>
       </c>
       <c r="O11">
-        <v>0.1031802120141343</v>
+        <v>2.78021582733813</v>
       </c>
       <c r="P11">
-        <v>0.292</v>
+        <v>15.3</v>
       </c>
       <c r="Q11">
-        <v>0.0006819243344231668</v>
+        <v>0.08905704307334109</v>
       </c>
       <c r="R11">
-        <v>0.1031802120141343</v>
+        <v>2.751798561151079</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>0.1579999999999995</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>0.01022124466295766</v>
       </c>
       <c r="U11">
-        <v>77.90000000000001</v>
+        <v>35.6</v>
       </c>
       <c r="V11">
-        <v>0.1819243344231668</v>
+        <v>0.2072176949941793</v>
       </c>
       <c r="W11">
-        <v>0.003808370340465617</v>
+        <v>0.01614401858304297</v>
       </c>
       <c r="X11">
-        <v>0.06727784244012448</v>
+        <v>0.1258396716901046</v>
       </c>
       <c r="Y11">
-        <v>-0.06346947209965886</v>
+        <v>-0.1096956531070617</v>
       </c>
       <c r="Z11">
-        <v>0.02471400820202892</v>
+        <v>0.1121327203677793</v>
       </c>
       <c r="AA11">
-        <v>0.01109266300287237</v>
+        <v>0.03364272035069556</v>
       </c>
       <c r="AB11">
-        <v>0.05328465119235436</v>
+        <v>0.0809023326689975</v>
       </c>
       <c r="AC11">
-        <v>-0.04219198818948199</v>
+        <v>-0.04725961231830194</v>
       </c>
       <c r="AD11">
-        <v>274.4</v>
+        <v>231.4</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>274.4</v>
+        <v>231.4</v>
       </c>
       <c r="AG11">
-        <v>196.5</v>
+        <v>195.8</v>
       </c>
       <c r="AH11">
-        <v>0.3905493879874751</v>
+        <v>0.5739087301587301</v>
       </c>
       <c r="AI11">
-        <v>0.2233800065125366</v>
+        <v>0.3520462498098281</v>
       </c>
       <c r="AJ11">
-        <v>0.3145509844725468</v>
+        <v>0.5326441784548422</v>
       </c>
       <c r="AK11">
-        <v>0.1707953063885267</v>
+        <v>0.3149428985041017</v>
       </c>
       <c r="AL11">
-        <v>7.41</v>
+        <v>8.31</v>
       </c>
       <c r="AM11">
-        <v>7.41</v>
+        <v>8.31</v>
       </c>
       <c r="AN11">
-        <v>16.4311377245509</v>
+        <v>10.06086956521739</v>
       </c>
       <c r="AO11">
-        <v>1.45748987854251</v>
+        <v>2.045728038507822</v>
       </c>
       <c r="AP11">
-        <v>11.76646706586826</v>
+        <v>8.513043478260871</v>
       </c>
       <c r="AQ11">
-        <v>1.45748987854251</v>
+        <v>2.045728038507822</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1874,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>First Investment Company K.S.C.P. (KWSE:ALOLA)</t>
+          <t>Rasiyat Holding Company K.P.S.C. (KWSE:RASIYAT)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1868,118 +1883,115 @@
         </is>
       </c>
       <c r="D12">
-        <v>-0.191</v>
+        <v>0.394</v>
       </c>
       <c r="G12">
-        <v>0.3693181818181818</v>
+        <v>0.3425742574257426</v>
       </c>
       <c r="H12">
-        <v>0.3693181818181818</v>
+        <v>0.3425742574257426</v>
       </c>
       <c r="I12">
-        <v>0.1125</v>
+        <v>0.08673267326732674</v>
       </c>
       <c r="J12">
-        <v>0.1125</v>
+        <v>0.08098878762048391</v>
       </c>
       <c r="K12">
-        <v>-2.81</v>
+        <v>0.226</v>
       </c>
       <c r="L12">
-        <v>-0.3991477272727273</v>
+        <v>0.02237623762376238</v>
       </c>
       <c r="M12">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="N12">
-        <v>8.058017727639001e-05</v>
+        <v>-0</v>
       </c>
       <c r="O12">
-        <v>-0.003558718861209964</v>
+        <v>-0</v>
       </c>
       <c r="P12">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="Q12">
-        <v>8.058017727639001e-05</v>
+        <v>-0</v>
       </c>
       <c r="R12">
-        <v>-0.003558718861209964</v>
+        <v>-0</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
       <c r="U12">
-        <v>40.3</v>
+        <v>1.6</v>
       </c>
       <c r="V12">
-        <v>0.3247381144238517</v>
+        <v>0.01934703748488513</v>
       </c>
       <c r="W12">
-        <v>-0.01919398907103825</v>
+        <v>0.006348314606741573</v>
       </c>
       <c r="X12">
-        <v>0.05112516461187042</v>
+        <v>0.08275449319960212</v>
       </c>
       <c r="Y12">
-        <v>-0.07031915368290867</v>
+        <v>-0.07640617859286056</v>
       </c>
       <c r="Z12">
-        <v>0.06100519930675909</v>
+        <v>0.2869318181818181</v>
       </c>
       <c r="AA12">
-        <v>0.006863084922010399</v>
+        <v>0.02323826008428657</v>
       </c>
       <c r="AB12">
-        <v>0.04922454943503009</v>
+        <v>0.07961657129409166</v>
       </c>
       <c r="AC12">
-        <v>-0.04236146451301969</v>
+        <v>-0.05637831120980509</v>
       </c>
       <c r="AD12">
-        <v>9.710000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>9.710000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="AG12">
-        <v>-30.59</v>
+        <v>6.49</v>
       </c>
       <c r="AH12">
-        <v>0.07256557805844108</v>
+        <v>0.08910672981605904</v>
       </c>
       <c r="AI12">
-        <v>0.05576934122106714</v>
+        <v>0.1481956402271478</v>
       </c>
       <c r="AJ12">
-        <v>-0.3271307881509999</v>
+        <v>0.07276600515752887</v>
       </c>
       <c r="AK12">
-        <v>-0.2286077273746356</v>
+        <v>0.122475938856388</v>
       </c>
       <c r="AL12">
-        <v>0.666</v>
+        <v>0.474</v>
       </c>
       <c r="AM12">
-        <v>0.666</v>
+        <v>0.474</v>
       </c>
       <c r="AN12">
-        <v>4.806930693069307</v>
+        <v>3.262096774193548</v>
       </c>
       <c r="AO12">
-        <v>1.189189189189189</v>
+        <v>1.848101265822785</v>
       </c>
       <c r="AP12">
-        <v>-15.14356435643564</v>
+        <v>2.616935483870968</v>
       </c>
       <c r="AQ12">
-        <v>1.189189189189189</v>
+        <v>1.848101265822785</v>
       </c>
     </row>
     <row r="13">
@@ -1999,7 +2011,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.175</v>
+        <v>-0.122</v>
+      </c>
+      <c r="E13">
+        <v>-0.168</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2014,85 +2029,85 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>-0.023</v>
+        <v>1.26</v>
       </c>
       <c r="L13">
-        <v>-0.003951890034364261</v>
+        <v>0.3134328358208955</v>
       </c>
       <c r="M13">
-        <v>1.356</v>
+        <v>11.13</v>
       </c>
       <c r="N13">
-        <v>0.03339901477832512</v>
+        <v>0.2754950495049505</v>
       </c>
       <c r="O13">
-        <v>-58.95652173913044</v>
+        <v>8.833333333333332</v>
       </c>
       <c r="P13">
-        <v>0.096</v>
+        <v>4.45</v>
       </c>
       <c r="Q13">
-        <v>0.002364532019704433</v>
+        <v>0.1101485148514852</v>
       </c>
       <c r="R13">
-        <v>-4.173913043478261</v>
+        <v>3.531746031746032</v>
       </c>
       <c r="S13">
-        <v>1.26</v>
+        <v>6.679999999999999</v>
       </c>
       <c r="T13">
-        <v>0.9292035398230087</v>
+        <v>0.6001796945193171</v>
       </c>
       <c r="U13">
-        <v>14.2</v>
+        <v>11.1</v>
       </c>
       <c r="V13">
-        <v>0.3497536945812807</v>
+        <v>0.2747524752475248</v>
       </c>
       <c r="W13">
-        <v>-0.0004085257548845471</v>
+        <v>0.0225</v>
       </c>
       <c r="X13">
-        <v>0.04941540894291111</v>
+        <v>0.07982336625758998</v>
       </c>
       <c r="Y13">
-        <v>-0.04982393469779565</v>
+        <v>-0.05732336625758998</v>
       </c>
       <c r="Z13">
-        <v>0.1106106391470437</v>
+        <v>0.09445710660494842</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.04908568609499474</v>
+        <v>0.07953786879626885</v>
       </c>
       <c r="AC13">
-        <v>-0.04908568609499474</v>
+        <v>-0.07953786879626885</v>
       </c>
       <c r="AD13">
-        <v>0.759</v>
+        <v>0.519</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>0.759</v>
+        <v>0.519</v>
       </c>
       <c r="AG13">
-        <v>-13.441</v>
+        <v>-10.581</v>
       </c>
       <c r="AH13">
-        <v>0.01835150753161343</v>
+        <v>0.01268359441824092</v>
       </c>
       <c r="AI13">
-        <v>0.01337232861748797</v>
+        <v>0.01122914818581103</v>
       </c>
       <c r="AJ13">
-        <v>-0.4949004013402554</v>
+        <v>-0.3548408732687213</v>
       </c>
       <c r="AK13">
-        <v>-0.3158203905166945</v>
+        <v>-0.3012899000541018</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2109,7 +2124,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bayan Investment Holding Company (K.S.C) Public (KWSE:BAYANINV)</t>
+          <t>Unicap Investment and Finance Company K.S.C.P. (KWSE:UNICAP)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2117,26 +2132,23 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D14">
-        <v>0.0152</v>
-      </c>
       <c r="G14">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>0.05044776119402986</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>0.04910637563626952</v>
+        <v>0</v>
       </c>
       <c r="K14">
-        <v>0.08</v>
+        <v>5.24</v>
       </c>
       <c r="L14">
-        <v>0.02388059701492537</v>
+        <v>0.3100591715976332</v>
       </c>
       <c r="M14">
         <v>-0</v>
@@ -2160,73 +2172,61 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>1.5</v>
+        <v>4.91</v>
       </c>
       <c r="V14">
-        <v>0.02555366269165247</v>
+        <v>0.1105855855855856</v>
       </c>
       <c r="W14">
-        <v>0.0007130124777183601</v>
+        <v>0.0801223241590214</v>
       </c>
       <c r="X14">
-        <v>0.05341776720862006</v>
+        <v>0.1567569101503737</v>
       </c>
       <c r="Y14">
-        <v>-0.0527047547309017</v>
+        <v>-0.07663458599135228</v>
       </c>
       <c r="Z14">
-        <v>0.02660567217046691</v>
+        <v>0.09418714819149528</v>
       </c>
       <c r="AA14">
-        <v>0.00130650813165839</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.05041870412819775</v>
+        <v>0.08797568452878113</v>
       </c>
       <c r="AC14">
-        <v>-0.04911219599653936</v>
+        <v>-0.08797568452878113</v>
       </c>
       <c r="AD14">
-        <v>9.279999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>9.279999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AG14">
-        <v>7.779999999999999</v>
+        <v>94.69</v>
       </c>
       <c r="AH14">
-        <v>0.136510738452486</v>
+        <v>0.6916666666666667</v>
       </c>
       <c r="AI14">
-        <v>0.04910572547359509</v>
+        <v>0.5521064301552107</v>
       </c>
       <c r="AJ14">
-        <v>0.1170276774969916</v>
+        <v>0.6807822273348192</v>
       </c>
       <c r="AK14">
-        <v>0.04149775976104118</v>
+        <v>0.539574904552966</v>
       </c>
       <c r="AL14">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="AM14">
-        <v>0.444</v>
-      </c>
-      <c r="AN14">
-        <v>14.34312210200927</v>
-      </c>
-      <c r="AO14">
-        <v>0.3806306306306306</v>
-      </c>
-      <c r="AP14">
-        <v>12.02472952086553</v>
-      </c>
-      <c r="AQ14">
-        <v>0.3806306306306306</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Asiya Capital Investments Company K.S.C.P. (KWSE:ASIYA)</t>
+          <t>Warba Capital Holding Company K.S.C.P. (KWSE:WARBACAP)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2245,26 +2245,23 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D15">
-        <v>0.202</v>
-      </c>
       <c r="G15">
-        <v>0</v>
+        <v>-0.1323809523809524</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>-0.1323809523809524</v>
       </c>
       <c r="I15">
-        <v>-0.1191176470588235</v>
+        <v>-0.3158730158730159</v>
       </c>
       <c r="J15">
-        <v>-0.1191176470588235</v>
+        <v>-0.3158730158730159</v>
       </c>
       <c r="K15">
-        <v>-0.554</v>
+        <v>-0.113</v>
       </c>
       <c r="L15">
-        <v>-0.1629411764705883</v>
+        <v>-0.03587301587301588</v>
       </c>
       <c r="M15">
         <v>-0</v>
@@ -2288,61 +2285,73 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>32.7</v>
+        <v>0.254</v>
       </c>
       <c r="V15">
-        <v>0.2449438202247191</v>
+        <v>0.009621212121212122</v>
       </c>
       <c r="W15">
-        <v>-0.002335581787521079</v>
+        <v>-0.004362934362934364</v>
       </c>
       <c r="X15">
-        <v>0.04887865283753826</v>
+        <v>0.08051172986935871</v>
       </c>
       <c r="Y15">
-        <v>-0.05121423462505933</v>
+        <v>-0.08487466423229308</v>
       </c>
       <c r="Z15">
-        <v>0.01720647773279352</v>
+        <v>0.1163306004874806</v>
       </c>
       <c r="AA15">
-        <v>-0.002049595141700405</v>
+        <v>-0.03674569761429943</v>
       </c>
       <c r="AB15">
-        <v>0.04887865283753826</v>
+        <v>0.07967235984395211</v>
       </c>
       <c r="AC15">
-        <v>-0.05092824797923866</v>
+        <v>-0.1164180574582515</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>0.866</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>0.866</v>
       </c>
       <c r="AG15">
-        <v>-32.7</v>
+        <v>0.612</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>0.03176116775471283</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>0.02919166722847704</v>
       </c>
       <c r="AJ15">
-        <v>-0.3244047619047619</v>
+        <v>0.02265659706796979</v>
       </c>
       <c r="AK15">
-        <v>-0.1570605187319885</v>
+        <v>0.0208078335373317</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>-0.763</v>
+      </c>
+      <c r="AN15">
+        <v>-2.261096605744125</v>
+      </c>
+      <c r="AO15">
+        <v>-23.69047619047619</v>
+      </c>
+      <c r="AP15">
+        <v>-1.597911227154047</v>
+      </c>
+      <c r="AQ15">
+        <v>1.304062909567497</v>
       </c>
     </row>
     <row r="16">
@@ -2353,7 +2362,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Unicap Investment and Finance Company K.S.C.P. (KWSE:UNICAP)</t>
+          <t>Ekttitab Holding Company K.S.C Public (KWSE:EKTTITAB)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2361,29 +2370,23 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D16">
-        <v>-0.0672</v>
-      </c>
-      <c r="E16">
-        <v>0.222</v>
-      </c>
       <c r="G16">
-        <v>0</v>
+        <v>-479.2307692307693</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>-479.2307692307693</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>-488.4615384615385</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>-488.4615384615385</v>
       </c>
       <c r="K16">
-        <v>9.199999999999999</v>
+        <v>-6.35</v>
       </c>
       <c r="L16">
-        <v>0.9340101522842639</v>
+        <v>-488.4615384615385</v>
       </c>
       <c r="M16">
         <v>-0</v>
@@ -2392,7 +2395,7 @@
         <v>-0</v>
       </c>
       <c r="O16">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P16">
         <v>-0</v>
@@ -2401,314 +2404,67 @@
         <v>-0</v>
       </c>
       <c r="R16">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S16">
         <v>0</v>
       </c>
       <c r="U16">
-        <v>6.03</v>
+        <v>0.019</v>
       </c>
       <c r="V16">
-        <v>0.1191699604743083</v>
+        <v>0.001759259259259259</v>
       </c>
       <c r="W16">
-        <v>0.1580756013745704</v>
+        <v>-0.1439909297052154</v>
       </c>
       <c r="X16">
-        <v>0.1123738418620926</v>
+        <v>0.07938024802941726</v>
       </c>
       <c r="Y16">
-        <v>0.04570175951247782</v>
+        <v>-0.2233711777346327</v>
       </c>
       <c r="Z16">
-        <v>0.07189781021897811</v>
+        <v>0.0002956494052898501</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>-0.1444133633531191</v>
       </c>
       <c r="AB16">
-        <v>0.05486397767816809</v>
+        <v>0.07938024802941726</v>
       </c>
       <c r="AC16">
-        <v>-0.05486397767816809</v>
+        <v>-0.2237936113825363</v>
       </c>
       <c r="AD16">
-        <v>111.9</v>
+        <v>0</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>111.9</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>105.87</v>
+        <v>-0.019</v>
       </c>
       <c r="AH16">
-        <v>0.6886153846153846</v>
+        <v>0</v>
       </c>
       <c r="AI16">
-        <v>0.578593588417787</v>
+        <v>0</v>
       </c>
       <c r="AJ16">
-        <v>0.6766153256215249</v>
+        <v>-0.001762359706891754</v>
       </c>
       <c r="AK16">
-        <v>0.5650317553503763</v>
+        <v>-0.0006152650497069396</v>
       </c>
       <c r="AL16">
         <v>0</v>
       </c>
       <c r="AM16">
         <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Kuwait</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Warba Capital Holding Company K.S.C.P. (KWSE:WARBACAP)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="D17">
-        <v>3.084</v>
-      </c>
-      <c r="G17">
-        <v>-0.2686170212765958</v>
-      </c>
-      <c r="H17">
-        <v>-0.2686170212765958</v>
-      </c>
-      <c r="I17">
-        <v>-0.5585106382978724</v>
-      </c>
-      <c r="J17">
-        <v>-0.5585106382978724</v>
-      </c>
-      <c r="K17">
-        <v>-0.801</v>
-      </c>
-      <c r="L17">
-        <v>-0.4260638297872341</v>
-      </c>
-      <c r="M17">
-        <v>-0</v>
-      </c>
-      <c r="N17">
-        <v>-0</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17">
-        <v>-0</v>
-      </c>
-      <c r="Q17">
-        <v>-0</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <v>0.282</v>
-      </c>
-      <c r="V17">
-        <v>0.009929577464788732</v>
-      </c>
-      <c r="W17">
-        <v>-0.03068965517241379</v>
-      </c>
-      <c r="X17">
-        <v>0.05035468481540393</v>
-      </c>
-      <c r="Y17">
-        <v>-0.08104433998781772</v>
-      </c>
-      <c r="Z17">
-        <v>0.06978470675575352</v>
-      </c>
-      <c r="AA17">
-        <v>-0.03897550111358575</v>
-      </c>
-      <c r="AB17">
-        <v>0.04930363828300388</v>
-      </c>
-      <c r="AC17">
-        <v>-0.08827913939658963</v>
-      </c>
-      <c r="AD17">
-        <v>1.46</v>
-      </c>
-      <c r="AE17">
-        <v>0</v>
-      </c>
-      <c r="AF17">
-        <v>1.46</v>
-      </c>
-      <c r="AG17">
-        <v>1.178</v>
-      </c>
-      <c r="AH17">
-        <v>0.04889484259879438</v>
-      </c>
-      <c r="AI17">
-        <v>0.0533625730994152</v>
-      </c>
-      <c r="AJ17">
-        <v>0.03982689837041044</v>
-      </c>
-      <c r="AK17">
-        <v>0.04350395154738164</v>
-      </c>
-      <c r="AL17">
-        <v>0.109</v>
-      </c>
-      <c r="AM17">
-        <v>-0.305</v>
-      </c>
-      <c r="AN17">
-        <v>-3.419203747072599</v>
-      </c>
-      <c r="AO17">
-        <v>-9.63302752293578</v>
-      </c>
-      <c r="AP17">
-        <v>-2.758782201405152</v>
-      </c>
-      <c r="AQ17">
-        <v>3.442622950819672</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Kuwait</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Al Salam Group Holding Company - K.S.C (Public) (KWSE:ALSALAM)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="G18">
-        <v>2.23021582733813</v>
-      </c>
-      <c r="H18">
-        <v>2.23021582733813</v>
-      </c>
-      <c r="I18">
-        <v>2.805755395683454</v>
-      </c>
-      <c r="J18">
-        <v>2.805755395683454</v>
-      </c>
-      <c r="K18">
-        <v>-24.4</v>
-      </c>
-      <c r="L18">
-        <v>4.388489208633094</v>
-      </c>
-      <c r="M18">
-        <v>-0</v>
-      </c>
-      <c r="N18">
-        <v>-0</v>
-      </c>
-      <c r="O18">
-        <v>0</v>
-      </c>
-      <c r="P18">
-        <v>-0</v>
-      </c>
-      <c r="Q18">
-        <v>-0</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="U18">
-        <v>0.04</v>
-      </c>
-      <c r="V18">
-        <v>0.001762114537444934</v>
-      </c>
-      <c r="W18">
-        <v>-0.2430278884462151</v>
-      </c>
-      <c r="X18">
-        <v>0.04887865283753826</v>
-      </c>
-      <c r="Y18">
-        <v>-0.2919065412837534</v>
-      </c>
-      <c r="Z18">
-        <v>-0.06229901285197261</v>
-      </c>
-      <c r="AA18">
-        <v>-0.174795791455175</v>
-      </c>
-      <c r="AB18">
-        <v>0.04887865283753826</v>
-      </c>
-      <c r="AC18">
-        <v>-0.2236744442927132</v>
-      </c>
-      <c r="AD18">
-        <v>0</v>
-      </c>
-      <c r="AE18">
-        <v>0</v>
-      </c>
-      <c r="AF18">
-        <v>0</v>
-      </c>
-      <c r="AG18">
-        <v>-0.04</v>
-      </c>
-      <c r="AH18">
-        <v>0</v>
-      </c>
-      <c r="AI18">
-        <v>0</v>
-      </c>
-      <c r="AJ18">
-        <v>-0.00176522506619594</v>
-      </c>
-      <c r="AK18">
-        <v>-0.0004856726566294318</v>
-      </c>
-      <c r="AL18">
-        <v>0</v>
-      </c>
-      <c r="AM18">
-        <v>0</v>
-      </c>
-      <c r="AN18">
-        <v>-0</v>
-      </c>
-      <c r="AP18">
-        <v>0.002666666666666667</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/kuwait/kuwait_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ16"/>
+  <dimension ref="A1:AQ18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.08810000000000001</v>
+        <v>0.0834</v>
       </c>
       <c r="E2">
-        <v>-0.025</v>
+        <v>0.0801</v>
       </c>
       <c r="G2">
-        <v>0.5042493988227451</v>
+        <v>0.4358626473331228</v>
       </c>
       <c r="H2">
-        <v>0.5042493988227451</v>
+        <v>0.4358626473331228</v>
       </c>
       <c r="I2">
-        <v>0.5213468529618944</v>
+        <v>0.3687334472396201</v>
       </c>
       <c r="J2">
-        <v>0.5135542678566242</v>
+        <v>0.3670722547265006</v>
       </c>
       <c r="K2">
-        <v>170.683</v>
+        <v>55.565</v>
       </c>
       <c r="L2">
-        <v>0.46065426437765</v>
+        <v>0.1339041500285569</v>
       </c>
       <c r="M2">
-        <v>66.788</v>
+        <v>69.31100000000001</v>
       </c>
       <c r="N2">
-        <v>0.03519789196310935</v>
+        <v>0.02915657075551069</v>
       </c>
       <c r="O2">
-        <v>0.3912984890117938</v>
+        <v>1.247385944389454</v>
       </c>
       <c r="P2">
-        <v>50.46</v>
+        <v>39.889</v>
       </c>
       <c r="Q2">
-        <v>0.02659288537549407</v>
+        <v>0.01677982500420663</v>
       </c>
       <c r="R2">
-        <v>0.2956357692330226</v>
+        <v>0.7178799604067309</v>
       </c>
       <c r="S2">
-        <v>16.328</v>
+        <v>29.422</v>
       </c>
       <c r="T2">
-        <v>0.2444750553991735</v>
+        <v>0.4244925047972183</v>
       </c>
       <c r="U2">
-        <v>251.032</v>
+        <v>299.366</v>
       </c>
       <c r="V2">
-        <v>0.1322961791831357</v>
+        <v>0.125932189130069</v>
       </c>
       <c r="W2">
-        <v>0.03762575527002435</v>
+        <v>0.03245847088439681</v>
       </c>
       <c r="X2">
-        <v>0.08415990584839494</v>
+        <v>0.07109289305927227</v>
       </c>
       <c r="Y2">
-        <v>-0.0465341505783706</v>
+        <v>-0.03863442217487546</v>
       </c>
       <c r="Z2">
-        <v>0.1205906590187752</v>
+        <v>0.126764366883836</v>
       </c>
       <c r="AA2">
-        <v>0.03662444954766091</v>
+        <v>0.01989856526049801</v>
       </c>
       <c r="AB2">
-        <v>0.07972793063253869</v>
+        <v>0.06821023085620125</v>
       </c>
       <c r="AC2">
-        <v>-0.04287141938319128</v>
+        <v>-0.04811103570606803</v>
       </c>
       <c r="AD2">
-        <v>779.715</v>
+        <v>700.86</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>779.715</v>
+        <v>700.86</v>
       </c>
       <c r="AG2">
-        <v>528.683</v>
+        <v>401.494</v>
       </c>
       <c r="AH2">
-        <v>0.2912410844851833</v>
+        <v>0.2276953665620553</v>
       </c>
       <c r="AI2">
-        <v>0.2169059299555041</v>
+        <v>0.1897364816208519</v>
       </c>
       <c r="AJ2">
-        <v>0.2179073054258479</v>
+        <v>0.1444901813585807</v>
       </c>
       <c r="AK2">
-        <v>0.158113971928559</v>
+        <v>0.1182780113913885</v>
       </c>
       <c r="AL2">
-        <v>23.265</v>
+        <v>35.432</v>
       </c>
       <c r="AM2">
-        <v>22.46</v>
+        <v>34.864</v>
       </c>
       <c r="AN2">
-        <v>4.531724951614872</v>
+        <v>3.125309360409894</v>
       </c>
       <c r="AO2">
-        <v>8.303073286052008</v>
+        <v>4.318412734251524</v>
       </c>
       <c r="AP2">
-        <v>3.07272008694793</v>
+        <v>1.790361778883672</v>
       </c>
       <c r="AQ2">
-        <v>8.6006678539626</v>
+        <v>4.388767783386874</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.051</v>
+        <v>0.109</v>
       </c>
       <c r="E3">
-        <v>0.262</v>
+        <v>0.377</v>
       </c>
       <c r="G3">
-        <v>0.5253955037468776</v>
+        <v>0.4067313177410153</v>
       </c>
       <c r="H3">
-        <v>0.5253955037468776</v>
+        <v>0.4067313177410153</v>
       </c>
       <c r="I3">
-        <v>0.5220649458784347</v>
+        <v>0.6719908727895036</v>
       </c>
       <c r="J3">
-        <v>0.5104248955044396</v>
+        <v>0.6577200988781137</v>
       </c>
       <c r="K3">
-        <v>58.4</v>
+        <v>109.2</v>
       </c>
       <c r="L3">
-        <v>0.4862614487926728</v>
+        <v>0.6229321163719338</v>
       </c>
       <c r="M3">
-        <v>7.71</v>
+        <v>8.35</v>
       </c>
       <c r="N3">
-        <v>0.02623341272541681</v>
+        <v>0.02229044313934864</v>
       </c>
       <c r="O3">
-        <v>0.1320205479452055</v>
+        <v>0.07646520146520146</v>
       </c>
       <c r="P3">
-        <v>7.71</v>
+        <v>8.35</v>
       </c>
       <c r="Q3">
-        <v>0.02623341272541681</v>
+        <v>0.02229044313934864</v>
       </c>
       <c r="R3">
-        <v>0.1320205479452055</v>
+        <v>0.07646520146520146</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>31.1</v>
+        <v>70.7</v>
       </c>
       <c r="V3">
-        <v>0.1058183055461041</v>
+        <v>0.1887346502936466</v>
       </c>
       <c r="W3">
-        <v>0.2102988836874325</v>
+        <v>0.4177505738332059</v>
       </c>
       <c r="X3">
-        <v>0.08556531849718776</v>
+        <v>0.07109240777051781</v>
       </c>
       <c r="Y3">
-        <v>0.1247335651902447</v>
+        <v>0.3466581660626881</v>
       </c>
       <c r="Z3">
-        <v>0.4038739617311767</v>
+        <v>0.6340881140128773</v>
       </c>
       <c r="AA3">
-        <v>0.2061473247135999</v>
+        <v>0.4170524970459863</v>
       </c>
       <c r="AB3">
-        <v>0.07978350142112527</v>
+        <v>0.06779262678553861</v>
       </c>
       <c r="AC3">
-        <v>0.1263638232924746</v>
+        <v>0.3492598702604477</v>
       </c>
       <c r="AD3">
-        <v>52.7</v>
+        <v>53.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>52.7</v>
+        <v>53.8</v>
       </c>
       <c r="AG3">
-        <v>21.6</v>
+        <v>-16.90000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.1520484708597807</v>
+        <v>0.1255835667600373</v>
       </c>
       <c r="AI3">
-        <v>0.1639701306782825</v>
+        <v>0.142478813559322</v>
       </c>
       <c r="AJ3">
-        <v>0.06846275752773376</v>
+        <v>-0.04724629577858542</v>
       </c>
       <c r="AK3">
-        <v>0.07440578711677576</v>
+        <v>-0.0550667970022809</v>
       </c>
       <c r="AL3">
-        <v>2.83</v>
+        <v>3.6</v>
       </c>
       <c r="AM3">
-        <v>2.83</v>
+        <v>3.6</v>
       </c>
       <c r="AN3">
-        <v>0.8247261345852895</v>
+        <v>0.4517212426532326</v>
       </c>
       <c r="AO3">
-        <v>22.15547703180212</v>
+        <v>32.72222222222222</v>
       </c>
       <c r="AP3">
-        <v>0.3380281690140846</v>
+        <v>-0.1418975650713687</v>
       </c>
       <c r="AQ3">
-        <v>22.15547703180212</v>
+        <v>32.72222222222222</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Asiya Capital Investments Company K.S.C.P. (KWSE:ASIYA)</t>
+          <t>International Financial Advisors Holding - KPSC (KWSE:IFA)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,25 +856,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.578</v>
+        <v>0.287</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.4130434782608696</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.4130434782608696</v>
       </c>
       <c r="I4">
-        <v>0.89086859688196</v>
+        <v>0.8297101449275361</v>
       </c>
       <c r="J4">
-        <v>0.8816696529743067</v>
+        <v>0.8212227429863049</v>
       </c>
       <c r="K4">
-        <v>39.5</v>
+        <v>43.3</v>
       </c>
       <c r="L4">
-        <v>0.8797327394209354</v>
+        <v>1.568840579710145</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -898,61 +898,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>5.88</v>
+        <v>5.31</v>
       </c>
       <c r="V4">
-        <v>0.04074844074844074</v>
+        <v>0.02131674026495383</v>
       </c>
       <c r="W4">
-        <v>0.1639684516396845</v>
+        <v>0.3452950558213716</v>
       </c>
       <c r="X4">
-        <v>0.07938024802941726</v>
+        <v>0.07631917198619029</v>
       </c>
       <c r="Y4">
-        <v>0.08458820361026725</v>
+        <v>0.2689758838351813</v>
       </c>
       <c r="Z4">
-        <v>0.2156580211335255</v>
+        <v>0.1276772910209557</v>
       </c>
       <c r="AA4">
-        <v>0.1901391326539211</v>
+        <v>0.10485149514929</v>
       </c>
       <c r="AB4">
-        <v>0.07938024802941726</v>
+        <v>0.0693270667347592</v>
       </c>
       <c r="AC4">
-        <v>0.1107588846245038</v>
+        <v>0.0355244284145308</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="AG4">
-        <v>-5.88</v>
+        <v>83.69</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.2632357290742384</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.2912303664921466</v>
       </c>
       <c r="AJ4">
-        <v>-0.04247941048981361</v>
+        <v>0.2514799122569789</v>
       </c>
       <c r="AK4">
-        <v>-0.02194684980591221</v>
+        <v>0.2786972593159945</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>5.66</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>5.66</v>
+      </c>
+      <c r="AN4">
+        <v>3.88646288209607</v>
+      </c>
+      <c r="AO4">
+        <v>4.045936395759717</v>
+      </c>
+      <c r="AP4">
+        <v>3.654585152838428</v>
+      </c>
+      <c r="AQ4">
+        <v>4.045936395759717</v>
       </c>
     </row>
     <row r="5">
@@ -972,7 +984,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.625</v>
+        <v>0.332</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -981,16 +993,16 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.825938566552901</v>
+        <v>0.7738461538461539</v>
       </c>
       <c r="J5">
-        <v>0.825938566552901</v>
+        <v>0.7701703846153846</v>
       </c>
       <c r="K5">
-        <v>3.93</v>
+        <v>3.99</v>
       </c>
       <c r="L5">
-        <v>0.6706484641638225</v>
+        <v>0.6138461538461539</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1014,67 +1026,67 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.8090000000000001</v>
+        <v>1.83</v>
       </c>
       <c r="V5">
-        <v>0.01688935281837161</v>
+        <v>0.02267657992565056</v>
       </c>
       <c r="W5">
-        <v>0.08204592901878915</v>
+        <v>0.09755501222493888</v>
       </c>
       <c r="X5">
-        <v>0.0991832396304116</v>
+        <v>0.07594541797996254</v>
       </c>
       <c r="Y5">
-        <v>-0.01713731061162245</v>
+        <v>0.02160959424497634</v>
       </c>
       <c r="Z5">
-        <v>0.08446238108965121</v>
+        <v>0.09616664940598599</v>
       </c>
       <c r="AA5">
-        <v>0.06976073796483137</v>
+        <v>0.07406470536018107</v>
       </c>
       <c r="AB5">
-        <v>0.08391269193467768</v>
+        <v>0.06801237020182375</v>
       </c>
       <c r="AC5">
-        <v>-0.01415195396984631</v>
+        <v>0.006052335158357319</v>
       </c>
       <c r="AD5">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="AG5">
-        <v>26.691</v>
+        <v>25.77</v>
       </c>
       <c r="AH5">
-        <v>0.3647214854111406</v>
+        <v>0.2548476454293629</v>
       </c>
       <c r="AI5">
-        <v>0.3973988439306358</v>
+        <v>0.3374083129584352</v>
       </c>
       <c r="AJ5">
-        <v>0.3578313737582282</v>
+        <v>0.2420400112707805</v>
       </c>
       <c r="AK5">
-        <v>0.3902706496468833</v>
+        <v>0.3222458421908216</v>
       </c>
       <c r="AL5">
-        <v>0.886</v>
+        <v>1.03</v>
       </c>
       <c r="AM5">
-        <v>0.886</v>
+        <v>1.03</v>
       </c>
       <c r="AO5">
-        <v>5.4627539503386</v>
+        <v>4.883495145631068</v>
       </c>
       <c r="AQ5">
-        <v>5.4627539503386</v>
+        <v>4.883495145631068</v>
       </c>
     </row>
     <row r="6">
@@ -1085,7 +1097,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kuwait and Middle East Financial Investment Company K.S.C.P. (KWSE:KMEFIC)</t>
+          <t>Rasiyat Holding Company-KPSC (KWSE:RASIYAT)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1093,119 +1105,113 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.117</v>
-      </c>
       <c r="G6">
-        <v>0.5125628140703518</v>
+        <v>0.2149253731343284</v>
       </c>
       <c r="H6">
-        <v>0.5125628140703518</v>
+        <v>0.2149253731343284</v>
       </c>
       <c r="I6">
-        <v>0.3331658291457287</v>
+        <v>0.1962686567164179</v>
       </c>
       <c r="J6">
-        <v>0.3314805545235908</v>
+        <v>0.1932729772191673</v>
       </c>
       <c r="K6">
-        <v>5.27</v>
+        <v>1.65</v>
       </c>
       <c r="L6">
-        <v>0.2648241206030151</v>
+        <v>0.1231343283582089</v>
       </c>
       <c r="M6">
-        <v>4.91</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.0724188790560472</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.9316888045540798</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>4.91</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.0724188790560472</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.9316888045540798</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>8.5</v>
+        <v>7.95</v>
       </c>
       <c r="V6">
-        <v>0.1253687315634218</v>
+        <v>0.06284584980237154</v>
       </c>
       <c r="W6">
-        <v>0.06288782816229117</v>
+        <v>0.04596100278551532</v>
       </c>
       <c r="X6">
-        <v>0.1412441777686587</v>
+        <v>0.06942009503534094</v>
       </c>
       <c r="Y6">
-        <v>-0.07835634960636752</v>
+        <v>-0.02345909224982562</v>
       </c>
       <c r="Z6">
-        <v>0.2157181571815718</v>
+        <v>0.3161122906345837</v>
       </c>
       <c r="AA6">
-        <v>0.07150637436335452</v>
+        <v>0.06109596354651668</v>
       </c>
       <c r="AB6">
-        <v>0.08735881124099966</v>
+        <v>0.06769811959756422</v>
       </c>
       <c r="AC6">
-        <v>-0.01585243687764513</v>
+        <v>-0.006602156051047539</v>
       </c>
       <c r="AD6">
-        <v>121.6</v>
+        <v>9.52</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>121.6</v>
+        <v>9.52</v>
       </c>
       <c r="AG6">
-        <v>113.1</v>
+        <v>1.569999999999999</v>
       </c>
       <c r="AH6">
-        <v>0.6420274551214361</v>
+        <v>0.06998970739597117</v>
       </c>
       <c r="AI6">
-        <v>0.5871559633027523</v>
+        <v>0.161301253812267</v>
       </c>
       <c r="AJ6">
-        <v>0.6252072968490879</v>
+        <v>0.01225892090263137</v>
       </c>
       <c r="AK6">
-        <v>0.5694864048338368</v>
+        <v>0.03074211866066183</v>
       </c>
       <c r="AL6">
-        <v>1.71</v>
+        <v>0.501</v>
       </c>
       <c r="AM6">
-        <v>1.71</v>
+        <v>0.501</v>
       </c>
       <c r="AN6">
-        <v>16.04221635883905</v>
+        <v>2.134529147982063</v>
       </c>
       <c r="AO6">
-        <v>3.87719298245614</v>
+        <v>5.249500998003992</v>
       </c>
       <c r="AP6">
-        <v>14.92084432717678</v>
+        <v>0.3520179372197308</v>
       </c>
       <c r="AQ6">
-        <v>3.87719298245614</v>
+        <v>5.249500998003992</v>
       </c>
     </row>
     <row r="7">
@@ -1216,7 +1222,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>International Financial Advisors Holding - KPSC (KWSE:IFA)</t>
+          <t>Tamdeen Investment Company - KSCP (KWSE:TAMINV)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1225,118 +1231,121 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.145</v>
+        <v>0.0834</v>
       </c>
       <c r="E7">
-        <v>-0.025</v>
+        <v>0.191</v>
       </c>
       <c r="G7">
-        <v>0.2655172413793104</v>
+        <v>0.8803278688524591</v>
       </c>
       <c r="H7">
-        <v>0.2655172413793104</v>
+        <v>0.8803278688524591</v>
       </c>
       <c r="I7">
-        <v>0.7931034482758621</v>
+        <v>0.8836065573770492</v>
       </c>
       <c r="J7">
-        <v>0.7751793103448277</v>
+        <v>0.8829089732528042</v>
       </c>
       <c r="K7">
-        <v>9.69</v>
+        <v>48.7</v>
       </c>
       <c r="L7">
-        <v>0.6682758620689655</v>
+        <v>0.798360655737705</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>14.17</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.03061136314538777</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>0.290965092402464</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>13.1</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.028299848779434</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0.2689938398357289</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.07</v>
+      </c>
+      <c r="T7">
+        <v>0.07551164431898379</v>
       </c>
       <c r="U7">
-        <v>2.83</v>
+        <v>52.9</v>
       </c>
       <c r="V7">
-        <v>0.03511166253101737</v>
+        <v>0.1142795420177144</v>
       </c>
       <c r="W7">
-        <v>0.1050976138828633</v>
+        <v>0.04864648886225152</v>
       </c>
       <c r="X7">
-        <v>0.1194368799552292</v>
+        <v>0.07109337834802675</v>
       </c>
       <c r="Y7">
-        <v>-0.01433926607236584</v>
+        <v>-0.02244688948577522</v>
       </c>
       <c r="Z7">
-        <v>0.07736634297300182</v>
+        <v>0.05996264622038729</v>
       </c>
       <c r="AA7">
-        <v>0.05997278838971295</v>
+        <v>0.05294155840796328</v>
       </c>
       <c r="AB7">
-        <v>0.0808052769230069</v>
+        <v>0.06841323615633915</v>
       </c>
       <c r="AC7">
-        <v>-0.02083248853329395</v>
+        <v>-0.01547167774837587</v>
       </c>
       <c r="AD7">
-        <v>93.59999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>93.59999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="AG7">
-        <v>90.77</v>
+        <v>13.6</v>
       </c>
       <c r="AH7">
-        <v>0.5373134328358209</v>
+        <v>0.1256139025311674</v>
       </c>
       <c r="AI7">
-        <v>0.4027538726333907</v>
+        <v>0.0576506285218899</v>
       </c>
       <c r="AJ7">
-        <v>0.5296726381513683</v>
+        <v>0.02854144805876181</v>
       </c>
       <c r="AK7">
-        <v>0.3953913838916235</v>
+        <v>0.01235689623841541</v>
       </c>
       <c r="AL7">
-        <v>2.02</v>
+        <v>3.88</v>
       </c>
       <c r="AM7">
-        <v>2.02</v>
+        <v>3.88</v>
       </c>
       <c r="AN7">
-        <v>8.139130434782608</v>
+        <v>1.110183639398998</v>
       </c>
       <c r="AO7">
-        <v>5.693069306930693</v>
+        <v>13.89175257731959</v>
       </c>
       <c r="AP7">
-        <v>7.89304347826087</v>
+        <v>0.2270450751252087</v>
       </c>
       <c r="AQ7">
-        <v>5.693069306930693</v>
+        <v>13.89175257731959</v>
       </c>
     </row>
     <row r="8">
@@ -1347,7 +1356,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tamdeen Investment Company - KSCP (KWSE:TAMINV)</t>
+          <t>Gulf Investment House - KPSC (KWSE:GIH)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1356,121 +1365,115 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.08810000000000001</v>
+        <v>0.4320000000000001</v>
       </c>
       <c r="E8">
-        <v>0.177</v>
+        <v>0.139</v>
       </c>
       <c r="G8">
-        <v>0.5567970204841712</v>
+        <v>0.02649350649350649</v>
       </c>
       <c r="H8">
-        <v>0.5567970204841712</v>
+        <v>0.02649350649350649</v>
       </c>
       <c r="I8">
-        <v>0.8733705772811917</v>
+        <v>0.1498701298701298</v>
       </c>
       <c r="J8">
-        <v>0.8680679702048416</v>
+        <v>0.1481298961298961</v>
       </c>
       <c r="K8">
-        <v>42</v>
+        <v>7.5</v>
       </c>
       <c r="L8">
-        <v>0.7821229050279329</v>
+        <v>0.1948051948051948</v>
       </c>
       <c r="M8">
-        <v>20.39</v>
+        <v>2.55</v>
       </c>
       <c r="N8">
-        <v>0.03054224086279209</v>
+        <v>0.005868814729574223</v>
       </c>
       <c r="O8">
-        <v>0.4854761904761905</v>
+        <v>0.34</v>
       </c>
       <c r="P8">
-        <v>10.9</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.01632714200119832</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>0.2595238095238095</v>
+        <v>-0</v>
       </c>
       <c r="S8">
-        <v>9.49</v>
+        <v>2.55</v>
       </c>
       <c r="T8">
-        <v>0.4654242275625307</v>
+        <v>1</v>
       </c>
       <c r="U8">
-        <v>118.9</v>
+        <v>30.1</v>
       </c>
       <c r="V8">
-        <v>0.1781006590772918</v>
+        <v>0.06927502876869966</v>
       </c>
       <c r="W8">
-        <v>0.04570184983677911</v>
+        <v>0.05458515283842794</v>
       </c>
       <c r="X8">
-        <v>0.0863605248156038</v>
+        <v>0.06806444447684087</v>
       </c>
       <c r="Y8">
-        <v>-0.04065867497882469</v>
+        <v>-0.01347929163841293</v>
       </c>
       <c r="Z8">
-        <v>0.04813984760197221</v>
+        <v>0.3159622486663931</v>
       </c>
       <c r="AA8">
-        <v>0.04178865979381443</v>
+        <v>0.04680345507592122</v>
       </c>
       <c r="AB8">
-        <v>0.08147182174715134</v>
+        <v>0.06770831086247858</v>
       </c>
       <c r="AC8">
-        <v>-0.03968316195333691</v>
+        <v>-0.02090485578655736</v>
       </c>
       <c r="AD8">
-        <v>135.1</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>135.1</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AG8">
-        <v>16.19999999999999</v>
+        <v>-21.48</v>
       </c>
       <c r="AH8">
-        <v>0.1683069639965118</v>
+        <v>0.01945296985015346</v>
       </c>
       <c r="AI8">
-        <v>0.1154700854700855</v>
+        <v>0.04970591627263291</v>
       </c>
       <c r="AJ8">
-        <v>0.02369113775957881</v>
+        <v>-0.05200716672316111</v>
       </c>
       <c r="AK8">
-        <v>0.01541242507848919</v>
+        <v>-0.1498744069215741</v>
       </c>
       <c r="AL8">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AN8">
-        <v>2.553875236294896</v>
-      </c>
-      <c r="AO8">
-        <v>7.328124999999999</v>
+        <v>1.260233918128655</v>
       </c>
       <c r="AP8">
-        <v>0.3062381852551983</v>
-      </c>
-      <c r="AQ8">
-        <v>7.328124999999999</v>
+        <v>-3.140350877192983</v>
       </c>
     </row>
     <row r="9">
@@ -1481,7 +1484,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Coast Investment &amp; Development Company K.S.C.P. (KWSE:COAST)</t>
+          <t>Kuwait Financial Centre - KPSC (KWSE:MARKAZ)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1490,115 +1493,121 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.213</v>
+        <v>-0.0254</v>
       </c>
       <c r="E9">
-        <v>-0.0173</v>
+        <v>0.0212</v>
       </c>
       <c r="G9">
-        <v>1.322645290581162</v>
+        <v>0.5643153526970954</v>
       </c>
       <c r="H9">
-        <v>1.322645290581162</v>
+        <v>0.5643153526970954</v>
       </c>
       <c r="I9">
-        <v>0.5501002004008017</v>
+        <v>0.2510373443983402</v>
       </c>
       <c r="J9">
-        <v>0.5464480828877673</v>
+        <v>0.2494293171692449</v>
       </c>
       <c r="K9">
-        <v>4.79</v>
+        <v>9.83</v>
       </c>
       <c r="L9">
-        <v>0.4799599198396793</v>
+        <v>0.2039419087136929</v>
       </c>
       <c r="M9">
-        <v>7.19</v>
+        <v>8.493</v>
       </c>
       <c r="N9">
-        <v>0.05643642072213501</v>
+        <v>0.05178658536585366</v>
       </c>
       <c r="O9">
-        <v>1.501043841336117</v>
+        <v>0.8639877924720244</v>
       </c>
       <c r="P9">
-        <v>7.19</v>
+        <v>8.16</v>
       </c>
       <c r="Q9">
-        <v>0.05643642072213501</v>
+        <v>0.04975609756097561</v>
       </c>
       <c r="R9">
-        <v>1.501043841336117</v>
+        <v>0.8301119023397762</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>0.3330000000000002</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>0.03920876015542214</v>
       </c>
       <c r="U9">
-        <v>3.13</v>
+        <v>34.9</v>
       </c>
       <c r="V9">
-        <v>0.02456828885400314</v>
+        <v>0.2128048780487805</v>
       </c>
       <c r="W9">
-        <v>0.02954966070326959</v>
+        <v>0.030006105006105</v>
       </c>
       <c r="X9">
-        <v>0.07938024802941726</v>
+        <v>0.09662062659421339</v>
       </c>
       <c r="Y9">
-        <v>-0.04983058732614767</v>
+        <v>-0.06661452158810838</v>
       </c>
       <c r="Z9">
-        <v>0.06716016150740242</v>
+        <v>0.09209017959495606</v>
       </c>
       <c r="AA9">
-        <v>0.03669954150215288</v>
+        <v>0.02296999061436302</v>
       </c>
       <c r="AB9">
-        <v>0.07938024802941726</v>
+        <v>0.06850186572920525</v>
       </c>
       <c r="AC9">
-        <v>-0.04268070652726438</v>
+        <v>-0.04553187511484223</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>194.7</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>194.7</v>
       </c>
       <c r="AG9">
-        <v>-3.13</v>
+        <v>159.8</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>0.5427934206858098</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>0.3465646137415451</v>
       </c>
       <c r="AJ9">
-        <v>-0.02518709262090609</v>
+        <v>0.493514515132798</v>
       </c>
       <c r="AK9">
-        <v>-0.02193873974907128</v>
+        <v>0.3032833554754223</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>11.9</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>11.9</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>11.3859649122807</v>
+      </c>
+      <c r="AO9">
+        <v>1.016806722689076</v>
       </c>
       <c r="AP9">
-        <v>-0.5670289855072465</v>
+        <v>9.345029239766079</v>
+      </c>
+      <c r="AQ9">
+        <v>1.016806722689076</v>
       </c>
     </row>
     <row r="10">
@@ -1609,7 +1618,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>First Investment Company K.S.C.P. (KWSE:ALOLA)</t>
+          <t>Coast Investment &amp; Development Company K.S.C.P. (KWSE:COAST)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1618,118 +1627,115 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.07719999999999999</v>
+        <v>-0.0848</v>
       </c>
       <c r="E10">
-        <v>-0.0322</v>
+        <v>-0.0301</v>
       </c>
       <c r="G10">
-        <v>0.08610619469026548</v>
+        <v>0.9808481532147744</v>
       </c>
       <c r="H10">
-        <v>0.08610619469026548</v>
+        <v>0.9808481532147744</v>
       </c>
       <c r="I10">
-        <v>0.4053097345132743</v>
+        <v>0.4295485636114911</v>
       </c>
       <c r="J10">
-        <v>0.4053097345132743</v>
+        <v>0.4295485636114911</v>
       </c>
       <c r="K10">
-        <v>1.28</v>
+        <v>5.09</v>
       </c>
       <c r="L10">
-        <v>0.1132743362831858</v>
+        <v>0.6963064295485636</v>
       </c>
       <c r="M10">
-        <v>-0</v>
+        <v>7.35</v>
       </c>
       <c r="N10">
-        <v>-0</v>
+        <v>0.07149805447470817</v>
       </c>
       <c r="O10">
-        <v>-0</v>
+        <v>1.444007858546169</v>
       </c>
       <c r="P10">
-        <v>-0</v>
+        <v>7.35</v>
       </c>
       <c r="Q10">
-        <v>-0</v>
+        <v>0.07149805447470817</v>
       </c>
       <c r="R10">
-        <v>-0</v>
+        <v>1.444007858546169</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
       <c r="U10">
-        <v>26.4</v>
+        <v>20.3</v>
       </c>
       <c r="V10">
-        <v>0.2885245901639344</v>
+        <v>0.1974708171206226</v>
       </c>
       <c r="W10">
-        <v>0.008210391276459268</v>
+        <v>0.03491083676268861</v>
       </c>
       <c r="X10">
-        <v>0.08267500936942318</v>
+        <v>0.06757914008240185</v>
       </c>
       <c r="Y10">
-        <v>-0.07446461809296391</v>
+        <v>-0.03266830331971323</v>
       </c>
       <c r="Z10">
-        <v>0.09017636262070065</v>
+        <v>0.0512371206280227</v>
       </c>
       <c r="AA10">
-        <v>0.03654935759316894</v>
+        <v>0.02200883156935585</v>
       </c>
       <c r="AB10">
-        <v>0.07961148983228711</v>
+        <v>0.06757914008240185</v>
       </c>
       <c r="AC10">
-        <v>-0.04306213223911817</v>
+        <v>-0.04557030851304599</v>
       </c>
       <c r="AD10">
-        <v>8.74</v>
+        <v>0</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>8.74</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>-17.66</v>
+        <v>-20.3</v>
       </c>
       <c r="AH10">
-        <v>0.08719074221867519</v>
+        <v>0</v>
       </c>
       <c r="AI10">
-        <v>0.04967602591792657</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
-        <v>-0.2391657638136511</v>
+        <v>-0.2460606060606061</v>
       </c>
       <c r="AK10">
-        <v>-0.1180954928447238</v>
+        <v>-0.1567567567567568</v>
       </c>
       <c r="AL10">
-        <v>0.593</v>
+        <v>0</v>
       </c>
       <c r="AM10">
-        <v>0.593</v>
+        <v>0</v>
       </c>
       <c r="AN10">
-        <v>1.571942446043166</v>
-      </c>
-      <c r="AO10">
-        <v>7.723440134907252</v>
+        <v>0</v>
       </c>
       <c r="AP10">
-        <v>-3.176258992805755</v>
-      </c>
-      <c r="AQ10">
-        <v>7.723440134907252</v>
+        <v>-6.383647798742138</v>
       </c>
     </row>
     <row r="11">
@@ -1740,7 +1746,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kuwait Financial Centre - KPSC (KWSE:MARKAZ)</t>
+          <t>First Investment Company K.S.C.P. (KWSE:ALOLA)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1749,121 +1755,118 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.0247</v>
-      </c>
-      <c r="E11">
-        <v>-0.273</v>
+        <v>-0.142</v>
       </c>
       <c r="G11">
-        <v>1.226381461675579</v>
+        <v>1.087777777777778</v>
       </c>
       <c r="H11">
-        <v>1.226381461675579</v>
+        <v>1.087777777777778</v>
       </c>
       <c r="I11">
-        <v>0.303030303030303</v>
+        <v>0.2922222222222222</v>
       </c>
       <c r="J11">
-        <v>0.3000259000259</v>
+        <v>0.2922222222222222</v>
       </c>
       <c r="K11">
-        <v>5.56</v>
+        <v>-79.40000000000001</v>
       </c>
       <c r="L11">
-        <v>0.09910873440285205</v>
+        <v>-8.822222222222223</v>
       </c>
       <c r="M11">
-        <v>15.458</v>
+        <v>0.007</v>
       </c>
       <c r="N11">
-        <v>0.089976717112922</v>
+        <v>0.0001313320825515947</v>
       </c>
       <c r="O11">
-        <v>2.78021582733813</v>
+        <v>-8.816120906801007e-05</v>
       </c>
       <c r="P11">
-        <v>15.3</v>
+        <v>0.007</v>
       </c>
       <c r="Q11">
-        <v>0.08905704307334109</v>
+        <v>0.0001313320825515947</v>
       </c>
       <c r="R11">
-        <v>2.751798561151079</v>
+        <v>-8.816120906801007e-05</v>
       </c>
       <c r="S11">
-        <v>0.1579999999999995</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>0.01022124466295766</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>35.6</v>
+        <v>21.6</v>
       </c>
       <c r="V11">
-        <v>0.2072176949941793</v>
+        <v>0.4052532833020638</v>
       </c>
       <c r="W11">
-        <v>0.01614401858304297</v>
+        <v>-0.4774503908598918</v>
       </c>
       <c r="X11">
-        <v>0.1258396716901046</v>
+        <v>0.07122323795137239</v>
       </c>
       <c r="Y11">
-        <v>-0.1096956531070617</v>
+        <v>-0.5486736288112641</v>
       </c>
       <c r="Z11">
-        <v>0.1121327203677793</v>
+        <v>0.06087250591816029</v>
       </c>
       <c r="AA11">
-        <v>0.03364272035069556</v>
+        <v>0.01778829895164017</v>
       </c>
       <c r="AB11">
-        <v>0.0809023326689975</v>
+        <v>0.06844006185073026</v>
       </c>
       <c r="AC11">
-        <v>-0.04725961231830194</v>
+        <v>-0.05065176289909008</v>
       </c>
       <c r="AD11">
-        <v>231.4</v>
+        <v>7.94</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>231.4</v>
+        <v>7.94</v>
       </c>
       <c r="AG11">
-        <v>195.8</v>
+        <v>-13.66</v>
       </c>
       <c r="AH11">
-        <v>0.5739087301587301</v>
+        <v>0.1296538210320052</v>
       </c>
       <c r="AI11">
-        <v>0.3520462498098281</v>
+        <v>0.08233098299460805</v>
       </c>
       <c r="AJ11">
-        <v>0.5326441784548422</v>
+        <v>-0.3446014127144298</v>
       </c>
       <c r="AK11">
-        <v>0.3149428985041017</v>
+        <v>-0.1825227151256013</v>
       </c>
       <c r="AL11">
-        <v>8.31</v>
+        <v>0.608</v>
       </c>
       <c r="AM11">
-        <v>8.31</v>
+        <v>0.608</v>
       </c>
       <c r="AN11">
-        <v>10.06086956521739</v>
+        <v>2.145945945945946</v>
       </c>
       <c r="AO11">
-        <v>2.045728038507822</v>
+        <v>4.325657894736842</v>
       </c>
       <c r="AP11">
-        <v>8.513043478260871</v>
+        <v>-3.691891891891892</v>
       </c>
       <c r="AQ11">
-        <v>2.045728038507822</v>
+        <v>4.325657894736842</v>
       </c>
     </row>
     <row r="12">
@@ -1874,7 +1877,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rasiyat Holding Company K.P.S.C. (KWSE:RASIYAT)</t>
+          <t>Ekttitab Holding Company K.S.C Public (KWSE:EKTTITAB)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1882,26 +1885,23 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D12">
-        <v>0.394</v>
-      </c>
       <c r="G12">
-        <v>0.3425742574257426</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>0.3425742574257426</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>0.08673267326732674</v>
+        <v>-0.2631578947368421</v>
       </c>
       <c r="J12">
-        <v>0.08098878762048391</v>
+        <v>-0.2631578947368421</v>
       </c>
       <c r="K12">
-        <v>0.226</v>
+        <v>-0.045</v>
       </c>
       <c r="L12">
-        <v>0.02237623762376238</v>
+        <v>-0.2631578947368421</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1910,7 +1910,7 @@
         <v>-0</v>
       </c>
       <c r="O12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P12">
         <v>-0</v>
@@ -1919,79 +1919,67 @@
         <v>-0</v>
       </c>
       <c r="R12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
       <c r="U12">
-        <v>1.6</v>
+        <v>0.006</v>
       </c>
       <c r="V12">
-        <v>0.01934703748488513</v>
+        <v>0.0003370786516853932</v>
       </c>
       <c r="W12">
-        <v>0.006348314606741573</v>
+        <v>-0.001451612903225806</v>
       </c>
       <c r="X12">
-        <v>0.08275449319960212</v>
+        <v>0.06757914008240185</v>
       </c>
       <c r="Y12">
-        <v>-0.07640617859286056</v>
+        <v>-0.06903075298562765</v>
       </c>
       <c r="Z12">
-        <v>0.2869318181818181</v>
+        <v>0.005519511958942578</v>
       </c>
       <c r="AA12">
-        <v>0.02323826008428657</v>
+        <v>-0.001452503147090152</v>
       </c>
       <c r="AB12">
-        <v>0.07961657129409166</v>
+        <v>0.06757914008240185</v>
       </c>
       <c r="AC12">
-        <v>-0.05637831120980509</v>
+        <v>-0.069031643229492</v>
       </c>
       <c r="AD12">
-        <v>8.09</v>
+        <v>0</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>8.09</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>6.49</v>
+        <v>-0.006</v>
       </c>
       <c r="AH12">
-        <v>0.08910672981605904</v>
+        <v>0</v>
       </c>
       <c r="AI12">
-        <v>0.1481956402271478</v>
+        <v>0</v>
       </c>
       <c r="AJ12">
-        <v>0.07276600515752887</v>
+        <v>-0.0003371923120152861</v>
       </c>
       <c r="AK12">
-        <v>0.122475938856388</v>
+        <v>-0.0001980590215884333</v>
       </c>
       <c r="AL12">
-        <v>0.474</v>
+        <v>0</v>
       </c>
       <c r="AM12">
-        <v>0.474</v>
-      </c>
-      <c r="AN12">
-        <v>3.262096774193548</v>
-      </c>
-      <c r="AO12">
-        <v>1.848101265822785</v>
-      </c>
-      <c r="AP12">
-        <v>2.616935483870968</v>
-      </c>
-      <c r="AQ12">
-        <v>1.848101265822785</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2011,10 +1999,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>-0.122</v>
+        <v>0.00209</v>
       </c>
       <c r="E13">
-        <v>-0.168</v>
+        <v>-0.0728</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2029,85 +2017,85 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>1.26</v>
+        <v>1.66</v>
       </c>
       <c r="L13">
-        <v>0.3134328358208955</v>
+        <v>0.3051470588235294</v>
       </c>
       <c r="M13">
-        <v>11.13</v>
+        <v>3.269</v>
       </c>
       <c r="N13">
-        <v>0.2754950495049505</v>
+        <v>0.08811320754716981</v>
       </c>
       <c r="O13">
-        <v>8.833333333333332</v>
+        <v>1.969277108433735</v>
       </c>
       <c r="P13">
-        <v>4.45</v>
+        <v>2.89</v>
       </c>
       <c r="Q13">
-        <v>0.1101485148514852</v>
+        <v>0.07789757412398922</v>
       </c>
       <c r="R13">
-        <v>3.531746031746032</v>
+        <v>1.740963855421687</v>
       </c>
       <c r="S13">
-        <v>6.679999999999999</v>
+        <v>0.379</v>
       </c>
       <c r="T13">
-        <v>0.6001796945193171</v>
+        <v>0.1159375955949832</v>
       </c>
       <c r="U13">
-        <v>11.1</v>
+        <v>7.52</v>
       </c>
       <c r="V13">
-        <v>0.2747524752475248</v>
+        <v>0.2026954177897574</v>
       </c>
       <c r="W13">
-        <v>0.0225</v>
+        <v>0.03632385120350109</v>
       </c>
       <c r="X13">
-        <v>0.07982336625758998</v>
+        <v>0.07793109761338979</v>
       </c>
       <c r="Y13">
-        <v>-0.05732336625758998</v>
+        <v>-0.0416072464098887</v>
       </c>
       <c r="Z13">
-        <v>0.09445710660494842</v>
+        <v>0.1549019049517355</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.07953786879626885</v>
+        <v>0.06955358079959706</v>
       </c>
       <c r="AC13">
-        <v>-0.07953786879626885</v>
+        <v>-0.06955358079959706</v>
       </c>
       <c r="AD13">
-        <v>0.519</v>
+        <v>15.7</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>0.519</v>
+        <v>15.7</v>
       </c>
       <c r="AG13">
-        <v>-10.581</v>
+        <v>8.18</v>
       </c>
       <c r="AH13">
-        <v>0.01268359441824092</v>
+        <v>0.2973484848484849</v>
       </c>
       <c r="AI13">
-        <v>0.01122914818581103</v>
+        <v>0.2679180887372014</v>
       </c>
       <c r="AJ13">
-        <v>-0.3548408732687213</v>
+        <v>0.1806537102473498</v>
       </c>
       <c r="AK13">
-        <v>-0.3012899000541018</v>
+        <v>0.1601409553641347</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2145,10 +2133,10 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>5.24</v>
+        <v>-4.08</v>
       </c>
       <c r="L14">
-        <v>0.3100591715976332</v>
+        <v>-0.2331428571428572</v>
       </c>
       <c r="M14">
         <v>-0</v>
@@ -2157,7 +2145,7 @@
         <v>-0</v>
       </c>
       <c r="O14">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P14">
         <v>-0</v>
@@ -2166,61 +2154,61 @@
         <v>-0</v>
       </c>
       <c r="R14">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
       <c r="U14">
-        <v>4.91</v>
+        <v>20.7</v>
       </c>
       <c r="V14">
-        <v>0.1105855855855856</v>
+        <v>0.3179723502304148</v>
       </c>
       <c r="W14">
-        <v>0.0801223241590214</v>
+        <v>-0.06355140186915888</v>
       </c>
       <c r="X14">
-        <v>0.1567569101503737</v>
+        <v>0.1001203459420885</v>
       </c>
       <c r="Y14">
-        <v>-0.07663458599135228</v>
+        <v>-0.1636717478112474</v>
       </c>
       <c r="Z14">
-        <v>0.09418714819149528</v>
+        <v>0.1099453414588176</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.08797568452878113</v>
+        <v>0.07136976383719815</v>
       </c>
       <c r="AC14">
-        <v>-0.08797568452878113</v>
+        <v>-0.07136976383719815</v>
       </c>
       <c r="AD14">
-        <v>99.59999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>99.59999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="AG14">
-        <v>94.69</v>
+        <v>65.89999999999999</v>
       </c>
       <c r="AH14">
-        <v>0.6916666666666667</v>
+        <v>0.5708635464733026</v>
       </c>
       <c r="AI14">
-        <v>0.5521064301552107</v>
+        <v>0.5368877867327959</v>
       </c>
       <c r="AJ14">
-        <v>0.6807822273348192</v>
+        <v>0.5030534351145037</v>
       </c>
       <c r="AK14">
-        <v>0.539574904552966</v>
+        <v>0.4687055476529161</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2245,32 +2233,35 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D15">
+        <v>1.031</v>
+      </c>
       <c r="G15">
-        <v>-0.1323809523809524</v>
+        <v>-0.3183150183150183</v>
       </c>
       <c r="H15">
-        <v>-0.1323809523809524</v>
+        <v>-0.3183150183150183</v>
       </c>
       <c r="I15">
-        <v>-0.3158730158730159</v>
+        <v>-0.5860805860805861</v>
       </c>
       <c r="J15">
-        <v>-0.3158730158730159</v>
+        <v>-0.5860805860805861</v>
       </c>
       <c r="K15">
-        <v>-0.113</v>
+        <v>-4.47</v>
       </c>
       <c r="L15">
-        <v>-0.03587301587301588</v>
+        <v>-1.637362637362637</v>
       </c>
       <c r="M15">
-        <v>-0</v>
+        <v>22.6</v>
       </c>
       <c r="N15">
-        <v>-0</v>
+        <v>2.173076923076923</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>-5.05592841163311</v>
       </c>
       <c r="P15">
         <v>-0</v>
@@ -2282,76 +2273,79 @@
         <v>0</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>22.6</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
       </c>
       <c r="U15">
-        <v>0.254</v>
+        <v>2.44</v>
       </c>
       <c r="V15">
-        <v>0.009621212121212122</v>
+        <v>0.2346153846153846</v>
       </c>
       <c r="W15">
-        <v>-0.004362934362934364</v>
+        <v>-0.1552083333333333</v>
       </c>
       <c r="X15">
-        <v>0.08051172986935871</v>
+        <v>0.06757914008240185</v>
       </c>
       <c r="Y15">
-        <v>-0.08487466423229308</v>
+        <v>-0.2227874734157352</v>
       </c>
       <c r="Z15">
-        <v>0.1163306004874806</v>
+        <v>0.09281925744594044</v>
       </c>
       <c r="AA15">
-        <v>-0.03674569761429943</v>
+        <v>-0.05439956480348158</v>
       </c>
       <c r="AB15">
-        <v>0.07967235984395211</v>
+        <v>0.06757914008240185</v>
       </c>
       <c r="AC15">
-        <v>-0.1164180574582515</v>
+        <v>-0.1219787048858834</v>
       </c>
       <c r="AD15">
-        <v>0.866</v>
+        <v>0</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>0.866</v>
+        <v>0</v>
       </c>
       <c r="AG15">
-        <v>0.612</v>
+        <v>-2.44</v>
       </c>
       <c r="AH15">
-        <v>0.03176116775471283</v>
+        <v>0</v>
       </c>
       <c r="AI15">
-        <v>0.02919166722847704</v>
+        <v>0</v>
       </c>
       <c r="AJ15">
-        <v>0.02265659706796979</v>
+        <v>-0.3065326633165829</v>
       </c>
       <c r="AK15">
-        <v>0.0208078335373317</v>
+        <v>-0.3185378590078329</v>
       </c>
       <c r="AL15">
-        <v>0.042</v>
+        <v>0.026</v>
       </c>
       <c r="AM15">
-        <v>-0.763</v>
+        <v>-0.5419999999999999</v>
       </c>
       <c r="AN15">
-        <v>-2.261096605744125</v>
+        <v>-0</v>
       </c>
       <c r="AO15">
-        <v>-23.69047619047619</v>
+        <v>-61.53846153846155</v>
       </c>
       <c r="AP15">
-        <v>-1.597911227154047</v>
+        <v>2.484725050916497</v>
       </c>
       <c r="AQ15">
-        <v>1.304062909567497</v>
+        <v>2.952029520295203</v>
       </c>
     </row>
     <row r="16">
@@ -2362,7 +2356,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ekttitab Holding Company K.S.C Public (KWSE:EKTTITAB)</t>
+          <t>Kuwait and Middle East Financial Investment Company K.S.C.P. (KWSE:KMEFIC)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2370,101 +2364,324 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G16">
-        <v>-479.2307692307693</v>
-      </c>
-      <c r="H16">
-        <v>-479.2307692307693</v>
-      </c>
-      <c r="I16">
-        <v>-488.4615384615385</v>
-      </c>
-      <c r="J16">
-        <v>-488.4615384615385</v>
-      </c>
       <c r="K16">
-        <v>-6.35</v>
-      </c>
-      <c r="L16">
-        <v>-488.4615384615385</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="M16">
-        <v>-0</v>
+        <v>0.029</v>
       </c>
       <c r="N16">
-        <v>-0</v>
+        <v>0.0005</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>-0.003098290598290599</v>
       </c>
       <c r="P16">
-        <v>-0</v>
+        <v>0.029</v>
       </c>
       <c r="Q16">
-        <v>-0</v>
+        <v>0.0005</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>-0.003098290598290599</v>
       </c>
       <c r="S16">
         <v>0</v>
       </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
       <c r="U16">
-        <v>0.019</v>
+        <v>7.84</v>
       </c>
       <c r="V16">
-        <v>0.001759259259259259</v>
+        <v>0.1351724137931034</v>
       </c>
       <c r="W16">
-        <v>-0.1439909297052154</v>
+        <v>-0.1140073081607795</v>
       </c>
       <c r="X16">
-        <v>0.07938024802941726</v>
+        <v>0.1253607066788793</v>
       </c>
       <c r="Y16">
-        <v>-0.2233711777346327</v>
+        <v>-0.2393680148396589</v>
       </c>
       <c r="Z16">
-        <v>0.0002956494052898501</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>-0.1444133633531191</v>
+        <v>-0.06506147540983606</v>
       </c>
       <c r="AB16">
-        <v>0.07938024802941726</v>
+        <v>0.07383814829958404</v>
       </c>
       <c r="AC16">
-        <v>-0.2237936113825363</v>
+        <v>-0.1388996237094201</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="AG16">
-        <v>-0.019</v>
+        <v>129.16</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>0.7025641025641025</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>0.6416861826697893</v>
       </c>
       <c r="AJ16">
-        <v>-0.001762359706891754</v>
+        <v>0.6901047232314597</v>
       </c>
       <c r="AK16">
-        <v>-0.0006152650497069396</v>
+        <v>0.6280268404162209</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>7.83</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>7.83</v>
+      </c>
+      <c r="AN16">
+        <v>-12.01754385964912</v>
+      </c>
+      <c r="AO16">
+        <v>-1.621966794380587</v>
+      </c>
+      <c r="AP16">
+        <v>-11.32982456140351</v>
+      </c>
+      <c r="AQ16">
+        <v>-1.621966794380587</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Asiya Capital Investments Company K.S.C.P. (KWSE:ASIYA)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K17">
+        <v>-57.6</v>
+      </c>
+      <c r="M17">
+        <v>2.49</v>
+      </c>
+      <c r="N17">
+        <v>0.02199646643109541</v>
+      </c>
+      <c r="O17">
+        <v>-0.04322916666666667</v>
+      </c>
+      <c r="P17">
+        <v>-0</v>
+      </c>
+      <c r="Q17">
+        <v>-0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>2.49</v>
+      </c>
+      <c r="T17">
+        <v>1</v>
+      </c>
+      <c r="U17">
+        <v>3.37</v>
+      </c>
+      <c r="V17">
+        <v>0.02977031802120141</v>
+      </c>
+      <c r="W17">
+        <v>-0.210372534696859</v>
+      </c>
+      <c r="X17">
+        <v>0.06757914008240185</v>
+      </c>
+      <c r="Y17">
+        <v>-0.2779516747792609</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>-0.21498954911914</v>
+      </c>
+      <c r="AB17">
+        <v>0.06757914008240185</v>
+      </c>
+      <c r="AC17">
+        <v>-0.2825686892015419</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>-3.37</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>-0.03068378402986434</v>
+      </c>
+      <c r="AK17">
+        <v>-0.01593908149269262</v>
+      </c>
+      <c r="AL17">
+        <v>0.055</v>
+      </c>
+      <c r="AM17">
+        <v>0.055</v>
+      </c>
+      <c r="AO17">
+        <v>-1047.272727272727</v>
+      </c>
+      <c r="AQ17">
+        <v>-1047.272727272727</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Bayan Investment Holding Company (K.S.C) Public (KWSE:BAYANINV)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>-0.115</v>
+      </c>
+      <c r="G18">
+        <v>-0.2359307359307359</v>
+      </c>
+      <c r="H18">
+        <v>-0.2359307359307359</v>
+      </c>
+      <c r="I18">
+        <v>-0.4090909090909091</v>
+      </c>
+      <c r="J18">
+        <v>-0.4090909090909091</v>
+      </c>
+      <c r="K18">
+        <v>-20.4</v>
+      </c>
+      <c r="L18">
+        <v>-8.83116883116883</v>
+      </c>
+      <c r="M18">
+        <v>0.003</v>
+      </c>
+      <c r="N18">
+        <v>0.0001102941176470588</v>
+      </c>
+      <c r="O18">
+        <v>-0.0001470588235294118</v>
+      </c>
+      <c r="P18">
+        <v>0.003</v>
+      </c>
+      <c r="Q18">
+        <v>0.0001102941176470588</v>
+      </c>
+      <c r="R18">
+        <v>-0.0001470588235294118</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>11.9</v>
+      </c>
+      <c r="V18">
+        <v>0.4375</v>
+      </c>
+      <c r="X18">
+        <v>0.07106861081739307</v>
+      </c>
+      <c r="AB18">
+        <v>0.06840809151057874</v>
+      </c>
+      <c r="AD18">
+        <v>3.88</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>3.88</v>
+      </c>
+      <c r="AG18">
+        <v>-8.02</v>
+      </c>
+      <c r="AH18">
+        <v>0.1248391248391248</v>
+      </c>
+      <c r="AI18">
+        <v>0.08383751080380293</v>
+      </c>
+      <c r="AJ18">
+        <v>-0.4181438998957247</v>
+      </c>
+      <c r="AK18">
+        <v>-0.2332751599767307</v>
+      </c>
+      <c r="AL18">
+        <v>0.342</v>
+      </c>
+      <c r="AM18">
+        <v>0.342</v>
+      </c>
+      <c r="AN18">
+        <v>-7.119266055045871</v>
+      </c>
+      <c r="AO18">
+        <v>-2.763157894736842</v>
+      </c>
+      <c r="AP18">
+        <v>14.71559633027523</v>
+      </c>
+      <c r="AQ18">
+        <v>-2.763157894736842</v>
       </c>
     </row>
   </sheetData>
